--- a/chair_all.xlsx
+++ b/chair_all.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/ファイル名変更セット/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:1_{367F8678-3549-4968-BC24-5D2798A0E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{795BCBFB-E852-4693-81DB-F526FBD74AA6}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{367F8678-3549-4968-BC24-5D2798A0E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{521F14BE-DE79-4C6D-A898-2CCF7453A836}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="561">
   <si>
     <t>シリーズ</t>
   </si>
@@ -2012,6 +2012,21 @@
   </si>
   <si>
     <t>No788</t>
+  </si>
+  <si>
+    <t>MC03</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オーク</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TIF期間限定</t>
+    <rPh sb="3" eb="7">
+      <t>キカンゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
@@ -2162,6 +2177,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2362,16 +2381,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1179"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:M1180"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.81640625" customWidth="1"/>
-    <col min="2" max="2" width="24.36328125" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" customWidth="1"/>
-    <col min="4" max="11" width="8.81640625" customWidth="1"/>
-    <col min="12" max="12" width="38.54296875" customWidth="1"/>
-    <col min="13" max="13" width="12.90625" customWidth="1"/>
-    <col min="14" max="28" width="8.81640625" customWidth="1"/>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" customWidth="1"/>
+    <col min="4" max="11" width="8.77734375" customWidth="1"/>
+    <col min="12" max="12" width="38.5546875" customWidth="1"/>
+    <col min="13" max="13" width="12.88671875" customWidth="1"/>
+    <col min="14" max="28" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="12.75" customHeight="1">
@@ -9198,48 +9217,36 @@
     </row>
     <row r="213" spans="1:13" ht="12.75" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B213" s="4" t="s">
-        <v>211</v>
+        <v>560</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>558</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D213" s="5">
-        <v>99</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D213" s="5"/>
       <c r="E213" s="5"/>
       <c r="F213" s="5"/>
-      <c r="G213" s="10">
-        <v>0</v>
-      </c>
-      <c r="H213" s="10">
-        <v>0</v>
-      </c>
-      <c r="I213" s="10">
-        <v>0</v>
-      </c>
-      <c r="J213" s="10">
-        <v>0</v>
-      </c>
-      <c r="K213" s="10">
-        <v>0</v>
-      </c>
+      <c r="G213" s="10"/>
+      <c r="H213" s="10"/>
+      <c r="I213" s="10"/>
+      <c r="J213" s="10"/>
+      <c r="K213" s="10"/>
       <c r="L213" s="3"/>
       <c r="M213" s="3" t="s">
-        <v>295</v>
+        <v>559</v>
       </c>
     </row>
     <row r="214" spans="1:13" ht="12.75" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B214" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B214" s="4" t="s">
         <v>211</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="D214" s="5">
         <v>99</v>
@@ -9263,52 +9270,50 @@
       </c>
       <c r="L214" s="3"/>
       <c r="M214" s="3" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="12.75" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B215" s="4" t="s">
-        <v>104</v>
+        <v>210</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C215" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D215" s="5" t="s">
-        <v>84</v>
+      <c r="D215" s="5">
+        <v>99</v>
       </c>
       <c r="E215" s="5"/>
       <c r="F215" s="5"/>
       <c r="G215" s="10">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H215" s="10">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="I215" s="10">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="J215" s="10">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="K215" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L215" s="3" t="s">
-        <v>85</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L215" s="3"/>
       <c r="M215" s="3" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="12.75" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B216" s="5" t="s">
-        <v>375</v>
+        <v>103</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>9</v>
@@ -9337,7 +9342,7 @@
         <v>85</v>
       </c>
       <c r="M216" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="12.75" customHeight="1">
@@ -9345,7 +9350,7 @@
         <v>123</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>9</v>
@@ -9374,76 +9379,78 @@
         <v>85</v>
       </c>
       <c r="M217" s="3" t="s">
-        <v>389</v>
+        <v>284</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="12.75" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B218" s="4" t="s">
-        <v>30</v>
+        <v>123</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E218" s="5"/>
       <c r="F218" s="5"/>
       <c r="G218" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H218" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I218" s="10">
         <v>18000</v>
       </c>
-      <c r="H218" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I218" s="10">
-        <v>24000</v>
-      </c>
       <c r="J218" s="10">
-        <v>38000</v>
+        <v>30000</v>
       </c>
       <c r="K218" s="10">
-        <v>42000</v>
+        <v>33000</v>
       </c>
       <c r="L218" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M218" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="M218" s="3" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="219" spans="1:13" ht="12.75" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="E219" s="5"/>
       <c r="F219" s="5"/>
       <c r="G219" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H219" s="10">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I219" s="10">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J219" s="10">
-        <v>30000</v>
+        <v>38000</v>
       </c>
       <c r="K219" s="10">
-        <v>33000</v>
+        <v>42000</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="M219" s="3"/>
     </row>
@@ -9452,7 +9459,7 @@
         <v>105</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>9</v>
@@ -9484,35 +9491,37 @@
     </row>
     <row r="221" spans="1:13" ht="12.75" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>167</v>
+        <v>105</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D221" s="5">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="D221" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E221" s="5"/>
       <c r="F221" s="5"/>
       <c r="G221" s="10">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="H221" s="10">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="I221" s="10">
-        <v>31000</v>
+        <v>18000</v>
       </c>
       <c r="J221" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K221" s="10">
-        <v>0</v>
-      </c>
-      <c r="L221" s="3"/>
+        <v>33000</v>
+      </c>
+      <c r="L221" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M221" s="3"/>
     </row>
     <row r="222" spans="1:13" ht="12.75" customHeight="1">
@@ -9520,7 +9529,7 @@
         <v>29</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>163</v>
@@ -9531,16 +9540,16 @@
       <c r="E222" s="5"/>
       <c r="F222" s="5"/>
       <c r="G222" s="10">
+        <v>24000</v>
+      </c>
+      <c r="H222" s="10">
         <v>26000</v>
       </c>
-      <c r="H222" s="10">
-        <v>28000</v>
-      </c>
       <c r="I222" s="10">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="J222" s="10">
-        <v>82000</v>
+        <v>80000</v>
       </c>
       <c r="K222" s="10">
         <v>0</v>
@@ -9550,13 +9559,13 @@
     </row>
     <row r="223" spans="1:13" ht="12.75" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="D223" s="5">
         <v>0</v>
@@ -9564,13 +9573,13 @@
       <c r="E223" s="5"/>
       <c r="F223" s="5"/>
       <c r="G223" s="10">
+        <v>26000</v>
+      </c>
+      <c r="H223" s="10">
         <v>28000</v>
       </c>
-      <c r="H223" s="10">
-        <v>29000</v>
-      </c>
       <c r="I223" s="10">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="J223" s="10">
         <v>82000</v>
@@ -9586,7 +9595,7 @@
         <v>105</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C224" s="3" t="s">
         <v>9</v>
@@ -9597,16 +9606,16 @@
       <c r="E224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="10">
-        <v>31000</v>
+        <v>28000</v>
       </c>
       <c r="H224" s="10">
-        <v>32000</v>
+        <v>29000</v>
       </c>
       <c r="I224" s="10">
-        <v>37000</v>
+        <v>34000</v>
       </c>
       <c r="J224" s="10">
-        <v>85000</v>
+        <v>82000</v>
       </c>
       <c r="K224" s="10">
         <v>0</v>
@@ -9619,7 +9628,7 @@
         <v>105</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>9</v>
@@ -9630,16 +9639,16 @@
       <c r="E225" s="5"/>
       <c r="F225" s="5"/>
       <c r="G225" s="10">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="H225" s="10">
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="I225" s="10">
-        <v>39000</v>
+        <v>37000</v>
       </c>
       <c r="J225" s="10">
-        <v>87000</v>
+        <v>85000</v>
       </c>
       <c r="K225" s="10">
         <v>0</v>
@@ -9649,47 +9658,43 @@
     </row>
     <row r="226" spans="1:13" ht="12.75" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B226" s="4" t="s">
-        <v>32</v>
+        <v>105</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D226" s="5" t="s">
-        <v>10</v>
+      <c r="D226" s="5">
+        <v>0</v>
       </c>
       <c r="E226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="10">
-        <v>18000</v>
+        <v>33000</v>
       </c>
       <c r="H226" s="10">
-        <v>20000</v>
+        <v>34000</v>
       </c>
       <c r="I226" s="10">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="J226" s="10">
-        <v>38000</v>
+        <v>87000</v>
       </c>
       <c r="K226" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L226" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M226" s="3" t="s">
-        <v>270</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L226" s="3"/>
+      <c r="M226" s="3"/>
     </row>
     <row r="227" spans="1:13" ht="12.75" customHeight="1">
       <c r="A227" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>310</v>
+        <v>32</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>9</v>
@@ -9726,33 +9731,33 @@
         <v>31</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>67</v>
+        <v>310</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E228" s="5"/>
       <c r="F228" s="5"/>
       <c r="G228" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="H228" s="10">
-        <v>49000</v>
+        <v>20000</v>
       </c>
       <c r="I228" s="10">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="J228" s="10">
-        <v>80000</v>
+        <v>38000</v>
       </c>
       <c r="K228" s="10">
-        <v>90000</v>
+        <v>42000</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="M228" s="3" t="s">
         <v>270</v>
@@ -9763,7 +9768,7 @@
         <v>31</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c r="C229" s="3" t="s">
         <v>43</v>
@@ -9797,36 +9802,36 @@
     </row>
     <row r="230" spans="1:13" ht="12.75" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>34</v>
+        <v>219</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E230" s="5"/>
       <c r="F230" s="5"/>
       <c r="G230" s="10">
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="H230" s="10">
-        <v>20000</v>
+        <v>49000</v>
       </c>
       <c r="I230" s="10">
-        <v>24000</v>
+        <v>53000</v>
       </c>
       <c r="J230" s="10">
-        <v>38000</v>
+        <v>80000</v>
       </c>
       <c r="K230" s="10">
-        <v>42000</v>
+        <v>90000</v>
       </c>
       <c r="L230" s="3" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="M230" s="3" t="s">
         <v>270</v>
@@ -9834,62 +9839,62 @@
     </row>
     <row r="231" spans="1:13" ht="12.75" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>344</v>
+        <v>34</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D231" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E231" s="5"/>
       <c r="F231" s="5"/>
-      <c r="G231" s="10"/>
-      <c r="H231" s="10"/>
-      <c r="I231" s="10"/>
-      <c r="J231" s="10"/>
-      <c r="K231" s="10"/>
-      <c r="L231" s="3"/>
+      <c r="G231" s="10">
+        <v>18000</v>
+      </c>
+      <c r="H231" s="10">
+        <v>20000</v>
+      </c>
+      <c r="I231" s="10">
+        <v>24000</v>
+      </c>
+      <c r="J231" s="10">
+        <v>38000</v>
+      </c>
+      <c r="K231" s="10">
+        <v>42000</v>
+      </c>
+      <c r="L231" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M231" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="232" spans="1:13" ht="12.75" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>35</v>
+        <v>345</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>220</v>
+        <v>344</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D232" s="5"/>
       <c r="E232" s="5"/>
       <c r="F232" s="5"/>
-      <c r="G232" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H232" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I232" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J232" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K232" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L232" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="G232" s="10"/>
+      <c r="H232" s="10"/>
+      <c r="I232" s="10"/>
+      <c r="J232" s="10"/>
+      <c r="K232" s="10"/>
+      <c r="L232" s="3"/>
       <c r="M232" s="3" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="12.75" customHeight="1">
@@ -9897,7 +9902,7 @@
         <v>35</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>9</v>
@@ -9934,33 +9939,33 @@
         <v>35</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E234" s="5"/>
       <c r="F234" s="5"/>
       <c r="G234" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="H234" s="10">
-        <v>49000</v>
+        <v>20000</v>
       </c>
       <c r="I234" s="10">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="J234" s="10">
-        <v>80000</v>
+        <v>38000</v>
       </c>
       <c r="K234" s="10">
-        <v>90000</v>
+        <v>42000</v>
       </c>
       <c r="L234" s="3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="M234" s="3" t="s">
         <v>12</v>
@@ -9971,7 +9976,7 @@
         <v>35</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>311</v>
+        <v>68</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>43</v>
@@ -10005,25 +10010,39 @@
     </row>
     <row r="236" spans="1:13" ht="12.75" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D236" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E236" s="5"/>
       <c r="F236" s="5"/>
-      <c r="G236" s="10"/>
-      <c r="H236" s="10"/>
-      <c r="I236" s="10"/>
-      <c r="J236" s="10"/>
-      <c r="K236" s="10"/>
-      <c r="L236" s="3"/>
+      <c r="G236" s="10">
+        <v>45000</v>
+      </c>
+      <c r="H236" s="10">
+        <v>49000</v>
+      </c>
+      <c r="I236" s="10">
+        <v>53000</v>
+      </c>
+      <c r="J236" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K236" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L236" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="M236" s="3" t="s">
-        <v>295</v>
+        <v>12</v>
       </c>
     </row>
     <row r="237" spans="1:13" ht="12.75" customHeight="1">
@@ -10031,7 +10050,7 @@
         <v>319</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C237" s="3" t="s">
         <v>233</v>
@@ -10054,7 +10073,7 @@
         <v>319</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>417</v>
+        <v>321</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>233</v>
@@ -10077,7 +10096,7 @@
         <v>319</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>233</v>
@@ -10097,10 +10116,10 @@
     </row>
     <row r="240" spans="1:13" ht="12.75" customHeight="1">
       <c r="A240" s="3" t="s">
-        <v>418</v>
+        <v>319</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>419</v>
+        <v>322</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>233</v>
@@ -10115,15 +10134,15 @@
       <c r="K240" s="10"/>
       <c r="L240" s="3"/>
       <c r="M240" s="3" t="s">
-        <v>420</v>
+        <v>295</v>
       </c>
     </row>
     <row r="241" spans="1:13" ht="12.75" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>323</v>
+        <v>418</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>313</v>
+        <v>419</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>233</v>
@@ -10138,7 +10157,7 @@
       <c r="K241" s="10"/>
       <c r="L241" s="3"/>
       <c r="M241" s="3" t="s">
-        <v>324</v>
+        <v>420</v>
       </c>
     </row>
     <row r="242" spans="1:13" ht="12.75" customHeight="1">
@@ -10146,7 +10165,7 @@
         <v>323</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>233</v>
@@ -10169,7 +10188,7 @@
         <v>323</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>233</v>
@@ -10189,47 +10208,33 @@
     </row>
     <row r="244" spans="1:13" ht="12.75" customHeight="1">
       <c r="A244" s="3" t="s">
-        <v>107</v>
+        <v>323</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D244" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D244" s="5"/>
       <c r="E244" s="5"/>
       <c r="F244" s="5"/>
-      <c r="G244" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H244" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I244" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J244" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K244" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L244" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G244" s="10"/>
+      <c r="H244" s="10"/>
+      <c r="I244" s="10"/>
+      <c r="J244" s="10"/>
+      <c r="K244" s="10"/>
+      <c r="L244" s="3"/>
       <c r="M244" s="3" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
     </row>
     <row r="245" spans="1:13" ht="12.75" customHeight="1">
       <c r="A245" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B245" s="5" t="s">
-        <v>250</v>
+      <c r="B245" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>9</v>
@@ -10266,20 +10271,34 @@
         <v>107</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D246" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E246" s="5"/>
       <c r="F246" s="5"/>
-      <c r="G246" s="10"/>
-      <c r="H246" s="10"/>
-      <c r="I246" s="10"/>
-      <c r="J246" s="10"/>
-      <c r="K246" s="10"/>
-      <c r="L246" s="3"/>
+      <c r="G246" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H246" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I246" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J246" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K246" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L246" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M246" s="3" t="s">
         <v>295</v>
       </c>
@@ -10289,7 +10308,7 @@
         <v>107</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>233</v>
@@ -10312,34 +10331,20 @@
         <v>107</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>252</v>
+        <v>421</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D248" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D248" s="5"/>
       <c r="E248" s="5"/>
       <c r="F248" s="5"/>
-      <c r="G248" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H248" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I248" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J248" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K248" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L248" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G248" s="10"/>
+      <c r="H248" s="10"/>
+      <c r="I248" s="10"/>
+      <c r="J248" s="10"/>
+      <c r="K248" s="10"/>
+      <c r="L248" s="3"/>
       <c r="M248" s="3" t="s">
         <v>295</v>
       </c>
@@ -10349,7 +10354,7 @@
         <v>107</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>437</v>
+        <v>252</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>9</v>
@@ -10382,69 +10387,69 @@
       </c>
     </row>
     <row r="250" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A250" s="3"/>
+      <c r="A250" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="B250" s="5" t="s">
-        <v>327</v>
+        <v>437</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D250" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E250" s="5"/>
       <c r="F250" s="5"/>
-      <c r="G250" s="10"/>
-      <c r="H250" s="10"/>
-      <c r="I250" s="10"/>
-      <c r="J250" s="10"/>
-      <c r="K250" s="10"/>
-      <c r="L250" s="3"/>
+      <c r="G250" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H250" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I250" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J250" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K250" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L250" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M250" s="3" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
     </row>
     <row r="251" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A251" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="A251" s="3"/>
       <c r="B251" s="5" t="s">
-        <v>120</v>
+        <v>327</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D251" s="5"/>
       <c r="E251" s="5"/>
       <c r="F251" s="5"/>
-      <c r="G251" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H251" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I251" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J251" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K251" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L251" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G251" s="10"/>
+      <c r="H251" s="10"/>
+      <c r="I251" s="10"/>
+      <c r="J251" s="10"/>
+      <c r="K251" s="10"/>
+      <c r="L251" s="3"/>
       <c r="M251" s="3" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="12.75" customHeight="1">
       <c r="A252" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>9</v>
@@ -10481,40 +10486,44 @@
         <v>126</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D253" s="5">
-        <v>0</v>
+      <c r="D253" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E253" s="5"/>
       <c r="F253" s="5"/>
       <c r="G253" s="10">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="H253" s="10">
-        <v>39000</v>
+        <v>16000</v>
       </c>
       <c r="I253" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="J253" s="10">
-        <v>99000</v>
+        <v>30000</v>
       </c>
       <c r="K253" s="10">
-        <v>0</v>
-      </c>
-      <c r="L253" s="3"/>
-      <c r="M253" s="3"/>
+        <v>33000</v>
+      </c>
+      <c r="L253" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M253" s="3" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="254" spans="1:13" ht="12.75" customHeight="1">
       <c r="A254" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>9</v>
@@ -10525,16 +10534,16 @@
       <c r="E254" s="5"/>
       <c r="F254" s="5"/>
       <c r="G254" s="10">
-        <v>40000</v>
+        <v>37000</v>
       </c>
       <c r="H254" s="10">
-        <v>42000</v>
+        <v>39000</v>
       </c>
       <c r="I254" s="10">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="J254" s="10">
-        <v>102000</v>
+        <v>99000</v>
       </c>
       <c r="K254" s="10">
         <v>0</v>
@@ -10544,47 +10553,43 @@
     </row>
     <row r="255" spans="1:13" ht="12.75" customHeight="1">
       <c r="A255" s="3" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D255" s="5" t="s">
-        <v>84</v>
+      <c r="D255" s="5">
+        <v>0</v>
       </c>
       <c r="E255" s="5"/>
       <c r="F255" s="5"/>
       <c r="G255" s="10">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="H255" s="10">
-        <v>16000</v>
+        <v>42000</v>
       </c>
       <c r="I255" s="10">
-        <v>18000</v>
+        <v>48000</v>
       </c>
       <c r="J255" s="10">
-        <v>30000</v>
+        <v>102000</v>
       </c>
       <c r="K255" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L255" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M255" s="3" t="s">
-        <v>295</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L255" s="3"/>
+      <c r="M255" s="3"/>
     </row>
     <row r="256" spans="1:13" ht="12.75" customHeight="1">
       <c r="A256" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>9</v>
@@ -10618,10 +10623,10 @@
     </row>
     <row r="257" spans="1:13" ht="12.75" customHeight="1">
       <c r="A257" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B257" s="11" t="s">
-        <v>460</v>
+        <v>108</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>9</v>
@@ -10650,15 +10655,15 @@
         <v>85</v>
       </c>
       <c r="M257" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="258" spans="1:13" ht="12.75" customHeight="1">
       <c r="A258" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B258" s="5" t="s">
-        <v>110</v>
+      <c r="B258" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>9</v>
@@ -10694,8 +10699,8 @@
       <c r="A259" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B259" s="11" t="s">
-        <v>111</v>
+      <c r="B259" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>9</v>
@@ -10729,31 +10734,47 @@
     </row>
     <row r="260" spans="1:13" ht="12.75" customHeight="1">
       <c r="A260" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B260" s="5" t="s">
-        <v>235</v>
+        <v>109</v>
+      </c>
+      <c r="B260" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D260" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
-      <c r="G260" s="10"/>
-      <c r="H260" s="10"/>
-      <c r="I260" s="10"/>
-      <c r="J260" s="10"/>
-      <c r="K260" s="10"/>
-      <c r="L260" s="3"/>
-      <c r="M260" s="3"/>
+      <c r="G260" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H260" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I260" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J260" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K260" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L260" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M260" s="3" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="261" spans="1:13" ht="12.75" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>329</v>
+        <v>235</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>175</v>
@@ -10767,16 +10788,14 @@
       <c r="J261" s="10"/>
       <c r="K261" s="10"/>
       <c r="L261" s="3"/>
-      <c r="M261" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="M261" s="3"/>
     </row>
     <row r="262" spans="1:13" ht="12.75" customHeight="1">
       <c r="A262" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>422</v>
+        <v>329</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>175</v>
@@ -10796,34 +10815,22 @@
     </row>
     <row r="263" spans="1:13" ht="12.75" customHeight="1">
       <c r="A263" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B263" s="4" t="s">
-        <v>213</v>
+        <v>330</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D263" s="5">
-        <v>99</v>
-      </c>
+      <c r="D263" s="5"/>
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
-      <c r="G263" s="10">
-        <v>0</v>
-      </c>
-      <c r="H263" s="10">
-        <v>0</v>
-      </c>
-      <c r="I263" s="10">
-        <v>0</v>
-      </c>
-      <c r="J263" s="10">
-        <v>0</v>
-      </c>
-      <c r="K263" s="10">
-        <v>0</v>
-      </c>
+      <c r="G263" s="10"/>
+      <c r="H263" s="10"/>
+      <c r="I263" s="10"/>
+      <c r="J263" s="10"/>
+      <c r="K263" s="10"/>
       <c r="L263" s="3"/>
       <c r="M263" s="3" t="s">
         <v>80</v>
@@ -10831,10 +10838,10 @@
     </row>
     <row r="264" spans="1:13" ht="12.75" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>175</v>
@@ -10866,22 +10873,34 @@
     </row>
     <row r="265" spans="1:13" ht="12.75" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D265" s="5"/>
+      <c r="D265" s="5">
+        <v>99</v>
+      </c>
       <c r="E265" s="5"/>
       <c r="F265" s="5"/>
-      <c r="G265" s="10"/>
-      <c r="H265" s="10"/>
-      <c r="I265" s="10"/>
-      <c r="J265" s="10"/>
-      <c r="K265" s="10"/>
+      <c r="G265" s="10">
+        <v>0</v>
+      </c>
+      <c r="H265" s="10">
+        <v>0</v>
+      </c>
+      <c r="I265" s="10">
+        <v>0</v>
+      </c>
+      <c r="J265" s="10">
+        <v>0</v>
+      </c>
+      <c r="K265" s="10">
+        <v>0</v>
+      </c>
       <c r="L265" s="3"/>
       <c r="M265" s="3" t="s">
         <v>80</v>
@@ -10892,7 +10911,7 @@
         <v>237</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>175</v>
@@ -10912,10 +10931,10 @@
     </row>
     <row r="267" spans="1:13" ht="12.75" customHeight="1">
       <c r="A267" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>175</v>
@@ -10930,44 +10949,30 @@
       <c r="K267" s="10"/>
       <c r="L267" s="3"/>
       <c r="M267" s="3" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="12.75" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>394</v>
+        <v>240</v>
+      </c>
+      <c r="B268" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="C268" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D268" s="5" t="s">
-        <v>148</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D268" s="5"/>
       <c r="E268" s="5"/>
       <c r="F268" s="5"/>
-      <c r="G268" s="10">
-        <v>26000</v>
-      </c>
-      <c r="H268" s="10">
-        <v>30000</v>
-      </c>
-      <c r="I268" s="10">
-        <v>34000</v>
-      </c>
-      <c r="J268" s="10">
-        <v>0</v>
-      </c>
-      <c r="K268" s="10">
-        <v>0</v>
-      </c>
-      <c r="L268" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="G268" s="10"/>
+      <c r="H268" s="10"/>
+      <c r="I268" s="10"/>
+      <c r="J268" s="10"/>
+      <c r="K268" s="10"/>
+      <c r="L268" s="3"/>
       <c r="M268" s="3" t="s">
-        <v>395</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="12.75" customHeight="1">
@@ -10975,7 +10980,7 @@
         <v>147</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>43</v>
@@ -11009,25 +11014,39 @@
     </row>
     <row r="270" spans="1:13" ht="12.75" customHeight="1">
       <c r="A270" s="3" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D270" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="E270" s="5"/>
       <c r="F270" s="5"/>
-      <c r="G270" s="10"/>
-      <c r="H270" s="10"/>
-      <c r="I270" s="10"/>
-      <c r="J270" s="10"/>
-      <c r="K270" s="10"/>
-      <c r="L270" s="3"/>
+      <c r="G270" s="10">
+        <v>26000</v>
+      </c>
+      <c r="H270" s="10">
+        <v>30000</v>
+      </c>
+      <c r="I270" s="10">
+        <v>34000</v>
+      </c>
+      <c r="J270" s="10">
+        <v>0</v>
+      </c>
+      <c r="K270" s="10">
+        <v>0</v>
+      </c>
+      <c r="L270" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="M270" s="3" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
     </row>
     <row r="271" spans="1:13" ht="12.75" customHeight="1">
@@ -11035,34 +11054,20 @@
         <v>69</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>256</v>
+        <v>331</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D271" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D271" s="5"/>
       <c r="E271" s="5"/>
       <c r="F271" s="5"/>
-      <c r="G271" s="10">
-        <v>45000</v>
-      </c>
-      <c r="H271" s="10">
-        <v>49000</v>
-      </c>
-      <c r="I271" s="10">
-        <v>53000</v>
-      </c>
-      <c r="J271" s="10">
-        <v>80000</v>
-      </c>
-      <c r="K271" s="10">
-        <v>90000</v>
-      </c>
-      <c r="L271" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="G271" s="10"/>
+      <c r="H271" s="10"/>
+      <c r="I271" s="10"/>
+      <c r="J271" s="10"/>
+      <c r="K271" s="10"/>
+      <c r="L271" s="3"/>
       <c r="M271" s="3" t="s">
         <v>270</v>
       </c>
@@ -11072,7 +11077,7 @@
         <v>69</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C272" s="3" t="s">
         <v>43</v>
@@ -11109,57 +11114,59 @@
         <v>69</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>332</v>
+        <v>255</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D273" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D273" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E273" s="5"/>
       <c r="F273" s="5"/>
-      <c r="G273" s="10"/>
-      <c r="H273" s="10"/>
-      <c r="I273" s="10"/>
-      <c r="J273" s="10"/>
-      <c r="K273" s="10"/>
-      <c r="L273" s="3"/>
+      <c r="G273" s="10">
+        <v>45000</v>
+      </c>
+      <c r="H273" s="10">
+        <v>49000</v>
+      </c>
+      <c r="I273" s="10">
+        <v>53000</v>
+      </c>
+      <c r="J273" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K273" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L273" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="M273" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="12.75" customHeight="1">
       <c r="A274" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>398</v>
+        <v>332</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="D274" s="5"/>
       <c r="E274" s="5"/>
       <c r="F274" s="5"/>
-      <c r="G274" s="10">
-        <v>42000</v>
-      </c>
-      <c r="H274" s="10">
-        <v>46000</v>
-      </c>
-      <c r="I274" s="10">
-        <v>50000</v>
-      </c>
-      <c r="J274" s="10">
-        <v>77000</v>
-      </c>
-      <c r="K274" s="10">
-        <v>87000</v>
-      </c>
-      <c r="L274" s="3" t="s">
-        <v>397</v>
-      </c>
+      <c r="G274" s="10"/>
+      <c r="H274" s="10"/>
+      <c r="I274" s="10"/>
+      <c r="J274" s="10"/>
+      <c r="K274" s="10"/>
+      <c r="L274" s="3"/>
       <c r="M274" s="3" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="12.75" customHeight="1">
@@ -11167,7 +11174,7 @@
         <v>70</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>455</v>
+        <v>398</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>43</v>
@@ -11202,34 +11209,34 @@
         <v>70</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="D276" s="5"/>
       <c r="E276" s="5"/>
       <c r="F276" s="5"/>
       <c r="G276" s="10">
-        <v>15000</v>
+        <v>42000</v>
       </c>
       <c r="H276" s="10">
-        <v>16000</v>
+        <v>46000</v>
       </c>
       <c r="I276" s="10">
-        <v>18000</v>
+        <v>50000</v>
       </c>
       <c r="J276" s="10">
-        <v>30000</v>
+        <v>77000</v>
       </c>
       <c r="K276" s="10">
-        <v>33000</v>
+        <v>87000</v>
       </c>
       <c r="L276" s="3" t="s">
-        <v>85</v>
+        <v>397</v>
       </c>
       <c r="M276" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="277" spans="1:13" ht="12.75" customHeight="1">
@@ -11237,14 +11244,12 @@
         <v>70</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>438</v>
+        <v>361</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D277" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D277" s="5"/>
       <c r="E277" s="5"/>
       <c r="F277" s="5"/>
       <c r="G277" s="10">
@@ -11274,10 +11279,10 @@
         <v>70</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>362</v>
+        <v>438</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D278" s="5" t="s">
         <v>84</v>
@@ -11285,22 +11290,22 @@
       <c r="E278" s="5"/>
       <c r="F278" s="5"/>
       <c r="G278" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H278" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I278" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J278" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K278" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L278" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="M278" s="3" t="s">
         <v>270</v>
@@ -11311,13 +11316,13 @@
         <v>70</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>439</v>
+        <v>362</v>
       </c>
       <c r="C279" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E279" s="5"/>
       <c r="F279" s="5"/>
@@ -11348,30 +11353,36 @@
         <v>70</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D280" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E280" s="5"/>
       <c r="F280" s="5"/>
       <c r="G280" s="10">
-        <v>13000</v>
+        <v>45000</v>
       </c>
       <c r="H280" s="10">
-        <v>14000</v>
+        <v>49000</v>
       </c>
       <c r="I280" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J280" s="10"/>
-      <c r="K280" s="10"/>
+        <v>53000</v>
+      </c>
+      <c r="J280" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K280" s="10">
+        <v>90000</v>
+      </c>
       <c r="L280" s="3" t="s">
-        <v>384</v>
+        <v>47</v>
       </c>
       <c r="M280" s="3" t="s">
-        <v>383</v>
+        <v>270</v>
       </c>
     </row>
     <row r="281" spans="1:13" ht="12.75" customHeight="1">
@@ -11379,7 +11390,7 @@
         <v>70</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="C281" s="3" t="s">
         <v>244</v>
@@ -11410,34 +11421,30 @@
         <v>70</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>43</v>
+        <v>244</v>
       </c>
       <c r="D282" s="5"/>
       <c r="E282" s="5"/>
       <c r="F282" s="5"/>
       <c r="G282" s="10">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="H282" s="10">
-        <v>42000</v>
+        <v>14000</v>
       </c>
       <c r="I282" s="10">
-        <v>46000</v>
-      </c>
-      <c r="J282" s="10">
-        <v>73000</v>
-      </c>
-      <c r="K282" s="10">
-        <v>83000</v>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="J282" s="10"/>
+      <c r="K282" s="10"/>
       <c r="L282" s="3" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="M282" s="3" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
     </row>
     <row r="283" spans="1:13" ht="12.75" customHeight="1">
@@ -11445,7 +11452,7 @@
         <v>70</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>456</v>
+        <v>399</v>
       </c>
       <c r="C283" s="3" t="s">
         <v>43</v>
@@ -11477,94 +11484,94 @@
     </row>
     <row r="284" spans="1:13" ht="12.75" customHeight="1">
       <c r="A284" s="3" t="s">
-        <v>339</v>
+        <v>70</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="D284" s="5"/>
       <c r="E284" s="5"/>
       <c r="F284" s="5"/>
-      <c r="G284" s="10"/>
-      <c r="H284" s="10"/>
-      <c r="I284" s="10"/>
-      <c r="J284" s="10"/>
-      <c r="K284" s="10"/>
-      <c r="L284" s="3"/>
+      <c r="G284" s="10">
+        <v>38000</v>
+      </c>
+      <c r="H284" s="10">
+        <v>42000</v>
+      </c>
+      <c r="I284" s="10">
+        <v>46000</v>
+      </c>
+      <c r="J284" s="10">
+        <v>73000</v>
+      </c>
+      <c r="K284" s="10">
+        <v>83000</v>
+      </c>
+      <c r="L284" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="M284" s="3" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
     </row>
     <row r="285" spans="1:13" ht="12.75" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B285" s="4" t="s">
-        <v>37</v>
+        <v>339</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D285" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D285" s="5"/>
       <c r="E285" s="5"/>
       <c r="F285" s="5"/>
-      <c r="G285" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H285" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I285" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J285" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K285" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L285" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="G285" s="10"/>
+      <c r="H285" s="10"/>
+      <c r="I285" s="10"/>
+      <c r="J285" s="10"/>
+      <c r="K285" s="10"/>
+      <c r="L285" s="3"/>
       <c r="M285" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="12.75" customHeight="1">
       <c r="A286" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B286" s="9" t="s">
-        <v>467</v>
+      <c r="B286" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D286" s="5"/>
+      <c r="D286" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E286" s="5"/>
       <c r="F286" s="5"/>
       <c r="G286" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H286" s="10">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I286" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="J286" s="10">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="K286" s="10">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="L286" s="3" t="s">
-        <v>363</v>
+        <v>11</v>
       </c>
       <c r="M286" s="3" t="s">
         <v>295</v>
@@ -11574,8 +11581,8 @@
       <c r="A287" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B287" s="4" t="s">
-        <v>364</v>
+      <c r="B287" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>9</v>
@@ -11584,68 +11591,66 @@
       <c r="E287" s="5"/>
       <c r="F287" s="5"/>
       <c r="G287" s="10">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H287" s="10">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="I287" s="10">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="J287" s="10">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="K287" s="10">
-        <v>31000</v>
-      </c>
-      <c r="L287" s="3"/>
+        <v>39000</v>
+      </c>
+      <c r="L287" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="M287" s="3" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="288" spans="1:13" ht="12.75" customHeight="1">
       <c r="A288" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>241</v>
+        <v>364</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D288" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D288" s="5"/>
       <c r="E288" s="5"/>
       <c r="F288" s="5"/>
       <c r="G288" s="10">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H288" s="10">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="I288" s="10">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="J288" s="10">
-        <v>38000</v>
+        <v>28000</v>
       </c>
       <c r="K288" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L288" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>31000</v>
+      </c>
+      <c r="L288" s="3"/>
       <c r="M288" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="12.75" customHeight="1">
       <c r="A289" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B289" s="11" t="s">
-        <v>242</v>
+      <c r="B289" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>9</v>
@@ -11679,39 +11684,39 @@
     </row>
     <row r="290" spans="1:13" ht="12.75" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="E290" s="5"/>
       <c r="F290" s="5"/>
       <c r="G290" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H290" s="10">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I290" s="10">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J290" s="10">
-        <v>30000</v>
+        <v>38000</v>
       </c>
       <c r="K290" s="10">
-        <v>33000</v>
+        <v>42000</v>
       </c>
       <c r="L290" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="M290" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="291" spans="1:13" ht="12.75" customHeight="1">
@@ -11719,7 +11724,7 @@
         <v>112</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>9</v>
@@ -11753,45 +11758,47 @@
     </row>
     <row r="292" spans="1:13" ht="12.75" customHeight="1">
       <c r="A292" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B292" s="5" t="s">
-        <v>72</v>
+        <v>112</v>
+      </c>
+      <c r="B292" s="11" t="s">
+        <v>258</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E292" s="5"/>
       <c r="F292" s="5"/>
       <c r="G292" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H292" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I292" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J292" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K292" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L292" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M292" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="M292" s="3" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="293" spans="1:13" ht="12.75" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>401</v>
+        <v>72</v>
       </c>
       <c r="C293" s="3" t="s">
         <v>43</v>
@@ -11826,7 +11833,7 @@
         <v>71</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>43</v>
@@ -11858,36 +11865,36 @@
     </row>
     <row r="295" spans="1:13" ht="12.75" customHeight="1">
       <c r="A295" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E295" s="5"/>
       <c r="F295" s="5"/>
       <c r="G295" s="10">
-        <v>32000</v>
+        <v>45000</v>
       </c>
       <c r="H295" s="10">
-        <v>36000</v>
+        <v>49000</v>
       </c>
       <c r="I295" s="10">
-        <v>40000</v>
+        <v>53000</v>
       </c>
       <c r="J295" s="10">
-        <v>67000</v>
+        <v>80000</v>
       </c>
       <c r="K295" s="10">
-        <v>77000</v>
+        <v>90000</v>
       </c>
       <c r="L295" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="M295" s="3"/>
     </row>
@@ -11895,34 +11902,34 @@
       <c r="A296" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B296" s="11" t="s">
-        <v>113</v>
+      <c r="B296" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E296" s="5"/>
       <c r="F296" s="5"/>
       <c r="G296" s="10">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H296" s="10">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="I296" s="10">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="J296" s="10">
-        <v>30000</v>
+        <v>67000</v>
       </c>
       <c r="K296" s="10">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="L296" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M296" s="3"/>
     </row>
@@ -11931,33 +11938,33 @@
         <v>38</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E297" s="5"/>
       <c r="F297" s="5"/>
       <c r="G297" s="10">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="H297" s="10">
-        <v>36000</v>
+        <v>16000</v>
       </c>
       <c r="I297" s="10">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="J297" s="10">
-        <v>67000</v>
+        <v>30000</v>
       </c>
       <c r="K297" s="10">
-        <v>77000</v>
+        <v>33000</v>
       </c>
       <c r="L297" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M297" s="3"/>
     </row>
@@ -11966,59 +11973,71 @@
         <v>38</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="5"/>
       <c r="G298" s="10">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H298" s="10">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="I298" s="10">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="J298" s="10">
-        <v>30000</v>
+        <v>67000</v>
       </c>
       <c r="K298" s="10">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="L298" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M298" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="M298" s="3"/>
     </row>
     <row r="299" spans="1:13" ht="12.75" customHeight="1">
       <c r="A299" s="3" t="s">
-        <v>335</v>
+        <v>38</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>336</v>
+        <v>114</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D299" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E299" s="5"/>
       <c r="F299" s="5"/>
-      <c r="G299" s="10"/>
-      <c r="H299" s="10"/>
-      <c r="I299" s="10"/>
-      <c r="J299" s="10"/>
-      <c r="K299" s="10"/>
-      <c r="L299" s="3"/>
+      <c r="G299" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H299" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I299" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J299" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K299" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L299" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M299" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="300" spans="1:13" ht="12.75" customHeight="1">
@@ -12026,7 +12045,7 @@
         <v>335</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>423</v>
+        <v>336</v>
       </c>
       <c r="C300" s="3" t="s">
         <v>233</v>
@@ -12049,7 +12068,7 @@
         <v>335</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>233</v>
@@ -12069,37 +12088,23 @@
     </row>
     <row r="302" spans="1:13" ht="12.75" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B302" s="5" t="s">
-        <v>115</v>
+        <v>335</v>
+      </c>
+      <c r="B302" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D302" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D302" s="5"/>
       <c r="E302" s="5"/>
       <c r="F302" s="5"/>
-      <c r="G302" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H302" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I302" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J302" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K302" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L302" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G302" s="10"/>
+      <c r="H302" s="10"/>
+      <c r="I302" s="10"/>
+      <c r="J302" s="10"/>
+      <c r="K302" s="10"/>
+      <c r="L302" s="3"/>
       <c r="M302" s="3" t="s">
         <v>284</v>
       </c>
@@ -12109,33 +12114,33 @@
         <v>73</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>402</v>
+        <v>115</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E303" s="5"/>
       <c r="F303" s="5"/>
       <c r="G303" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H303" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I303" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J303" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K303" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L303" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="M303" s="3" t="s">
         <v>284</v>
@@ -12146,7 +12151,7 @@
         <v>73</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>457</v>
+        <v>402</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>43</v>
@@ -12183,7 +12188,7 @@
         <v>73</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>74</v>
+        <v>457</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>43</v>
@@ -12220,7 +12225,7 @@
         <v>73</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>458</v>
+        <v>74</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>43</v>
@@ -12254,36 +12259,36 @@
     </row>
     <row r="307" spans="1:13" ht="12.75" customHeight="1">
       <c r="A307" s="3" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>117</v>
+        <v>458</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="E307" s="5"/>
       <c r="F307" s="5"/>
       <c r="G307" s="10">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="H307" s="10">
-        <v>16000</v>
+        <v>49000</v>
       </c>
       <c r="I307" s="10">
-        <v>18000</v>
+        <v>53000</v>
       </c>
       <c r="J307" s="10">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="K307" s="10">
-        <v>33000</v>
+        <v>90000</v>
       </c>
       <c r="L307" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="M307" s="3" t="s">
         <v>284</v>
@@ -12294,13 +12299,13 @@
         <v>116</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>365</v>
+        <v>117</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E308" s="5"/>
       <c r="F308" s="5"/>
@@ -12331,13 +12336,13 @@
         <v>116</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>441</v>
+        <v>365</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E309" s="5"/>
       <c r="F309" s="5"/>
@@ -12365,10 +12370,10 @@
     </row>
     <row r="310" spans="1:13" ht="12.75" customHeight="1">
       <c r="A310" s="3" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>118</v>
+        <v>441</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>9</v>
@@ -12402,83 +12407,97 @@
     </row>
     <row r="311" spans="1:13" ht="12.75" customHeight="1">
       <c r="A311" s="3" t="s">
-        <v>333</v>
+        <v>73</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>334</v>
+        <v>118</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D311" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D311" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E311" s="5"/>
       <c r="F311" s="5"/>
-      <c r="G311" s="10"/>
-      <c r="H311" s="10"/>
-      <c r="I311" s="10"/>
-      <c r="J311" s="10"/>
-      <c r="K311" s="10"/>
-      <c r="L311" s="3"/>
+      <c r="G311" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H311" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I311" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J311" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K311" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L311" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M311" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="312" spans="1:13" ht="12.75" customHeight="1">
       <c r="A312" s="3" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="D312" s="5"/>
       <c r="E312" s="5"/>
       <c r="F312" s="5"/>
-      <c r="G312" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H312" s="10">
-        <v>17000</v>
-      </c>
-      <c r="I312" s="10">
-        <v>21000</v>
-      </c>
-      <c r="J312" s="10">
-        <v>35000</v>
-      </c>
-      <c r="K312" s="10">
-        <v>39000</v>
-      </c>
-      <c r="L312" s="3" t="s">
-        <v>363</v>
-      </c>
+      <c r="G312" s="10"/>
+      <c r="H312" s="10"/>
+      <c r="I312" s="10"/>
+      <c r="J312" s="10"/>
+      <c r="K312" s="10"/>
+      <c r="L312" s="3"/>
       <c r="M312" s="3" t="s">
-        <v>367</v>
+        <v>284</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="12.75" customHeight="1">
       <c r="A313" s="3" t="s">
-        <v>265</v>
+        <v>366</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>259</v>
+        <v>368</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
       <c r="F313" s="5"/>
-      <c r="G313" s="10"/>
-      <c r="H313" s="10"/>
-      <c r="I313" s="10"/>
-      <c r="J313" s="10"/>
-      <c r="K313" s="10"/>
-      <c r="L313" s="3"/>
+      <c r="G313" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H313" s="10">
+        <v>17000</v>
+      </c>
+      <c r="I313" s="10">
+        <v>21000</v>
+      </c>
+      <c r="J313" s="10">
+        <v>35000</v>
+      </c>
+      <c r="K313" s="10">
+        <v>39000</v>
+      </c>
+      <c r="L313" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="M313" s="3" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="12.75" customHeight="1">
@@ -12486,7 +12505,7 @@
         <v>265</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>233</v>
@@ -12509,7 +12528,7 @@
         <v>265</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>233</v>
@@ -12528,12 +12547,14 @@
       </c>
     </row>
     <row r="316" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A316" s="3"/>
+      <c r="A316" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="B316" s="5" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C316" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D316" s="5"/>
       <c r="E316" s="5"/>
@@ -12544,12 +12565,14 @@
       <c r="J316" s="10"/>
       <c r="K316" s="10"/>
       <c r="L316" s="3"/>
-      <c r="M316" s="3"/>
+      <c r="M316" s="3" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="317" spans="1:13" ht="12.75" customHeight="1">
       <c r="A317" s="3"/>
       <c r="B317" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C317" s="3" t="s">
         <v>244</v>
@@ -12568,7 +12591,7 @@
     <row r="318" spans="1:13" ht="12.75" customHeight="1">
       <c r="A318" s="3"/>
       <c r="B318" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>244</v>
@@ -12587,7 +12610,7 @@
     <row r="319" spans="1:13" ht="12.75" customHeight="1">
       <c r="A319" s="3"/>
       <c r="B319" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>244</v>
@@ -12604,48 +12627,30 @@
       <c r="M319" s="3"/>
     </row>
     <row r="320" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A320" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B320" s="4" t="s">
-        <v>314</v>
+      <c r="A320" s="3"/>
+      <c r="B320" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="C320" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D320" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D320" s="5"/>
       <c r="E320" s="5"/>
       <c r="F320" s="5"/>
-      <c r="G320" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H320" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I320" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J320" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K320" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L320" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M320" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="G320" s="10"/>
+      <c r="H320" s="10"/>
+      <c r="I320" s="10"/>
+      <c r="J320" s="10"/>
+      <c r="K320" s="10"/>
+      <c r="L320" s="3"/>
+      <c r="M320" s="3"/>
     </row>
     <row r="321" spans="1:13" ht="12.75" customHeight="1">
       <c r="A321" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C321" s="3" t="s">
         <v>9</v>
@@ -12682,7 +12687,7 @@
         <v>39</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>9</v>
@@ -12716,72 +12721,72 @@
     </row>
     <row r="323" spans="1:13" ht="12.75" customHeight="1">
       <c r="A323" s="3" t="s">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>216</v>
+        <v>316</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D323" s="5">
-        <v>99</v>
+      <c r="D323" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E323" s="5"/>
       <c r="F323" s="5"/>
       <c r="G323" s="10">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="H323" s="10">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I323" s="10">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="J323" s="10">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="K323" s="10">
-        <v>0</v>
-      </c>
-      <c r="L323" s="3"/>
+        <v>42000</v>
+      </c>
+      <c r="L323" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M323" s="3" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
     </row>
     <row r="324" spans="1:13" ht="12.75" customHeight="1">
       <c r="A324" s="3" t="s">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D324" s="5" t="s">
-        <v>10</v>
+      <c r="D324" s="5">
+        <v>99</v>
       </c>
       <c r="E324" s="5"/>
       <c r="F324" s="5"/>
       <c r="G324" s="10">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="H324" s="10">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I324" s="10">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="J324" s="10">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="K324" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L324" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L324" s="3"/>
       <c r="M324" s="3" t="s">
         <v>217</v>
       </c>
@@ -12791,7 +12796,7 @@
         <v>40</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>9</v>
@@ -12825,134 +12830,136 @@
     </row>
     <row r="326" spans="1:13" ht="12.75" customHeight="1">
       <c r="A326" s="3" t="s">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="C326" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D326" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E326" s="5"/>
       <c r="F326" s="5"/>
-      <c r="G326" s="10"/>
-      <c r="H326" s="10"/>
-      <c r="I326" s="10"/>
-      <c r="J326" s="10"/>
-      <c r="K326" s="10"/>
-      <c r="L326" s="3"/>
-      <c r="M326" s="3"/>
+      <c r="G326" s="10">
+        <v>18000</v>
+      </c>
+      <c r="H326" s="10">
+        <v>20000</v>
+      </c>
+      <c r="I326" s="10">
+        <v>24000</v>
+      </c>
+      <c r="J326" s="10">
+        <v>38000</v>
+      </c>
+      <c r="K326" s="10">
+        <v>42000</v>
+      </c>
+      <c r="L326" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M326" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="327" spans="1:13" ht="12.75" customHeight="1">
       <c r="A327" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B327" s="5" t="s">
-        <v>343</v>
+        <v>248</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D327" s="5"/>
       <c r="E327" s="5"/>
       <c r="F327" s="5"/>
-      <c r="G327" s="10">
-        <v>13000</v>
-      </c>
-      <c r="H327" s="10">
-        <v>14000</v>
-      </c>
-      <c r="I327" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J327" s="10">
-        <v>28000</v>
-      </c>
-      <c r="K327" s="10">
-        <v>31000</v>
-      </c>
+      <c r="G327" s="10"/>
+      <c r="H327" s="10"/>
+      <c r="I327" s="10"/>
+      <c r="J327" s="10"/>
+      <c r="K327" s="10"/>
       <c r="L327" s="3"/>
-      <c r="M327" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="M327" s="3"/>
     </row>
     <row r="328" spans="1:13" ht="12.75" customHeight="1">
       <c r="A328" s="3" t="s">
-        <v>121</v>
+        <v>341</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>122</v>
+        <v>343</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D328" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D328" s="5"/>
       <c r="E328" s="5"/>
       <c r="F328" s="5"/>
       <c r="G328" s="10">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H328" s="10">
+        <v>14000</v>
+      </c>
+      <c r="I328" s="10">
         <v>16000</v>
       </c>
-      <c r="I328" s="10">
-        <v>18000</v>
-      </c>
       <c r="J328" s="10">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="K328" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L328" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M328" s="3"/>
+        <v>31000</v>
+      </c>
+      <c r="L328" s="3"/>
+      <c r="M328" s="3" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="329" spans="1:13" ht="12.75" customHeight="1">
       <c r="A329" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B329" s="4" t="s">
-        <v>371</v>
+        <v>121</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="C329" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D329" s="5"/>
+      <c r="D329" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E329" s="5"/>
       <c r="F329" s="5"/>
       <c r="G329" s="10">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H329" s="10">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="I329" s="10">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="J329" s="10">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="K329" s="10">
-        <v>28000</v>
-      </c>
-      <c r="L329" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="M329" s="15" t="s">
-        <v>385</v>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="L329" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M329" s="3"/>
     </row>
     <row r="330" spans="1:13" ht="12.75" customHeight="1">
       <c r="A330" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>442</v>
+        <v>371</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>9</v>
@@ -12979,15 +12986,15 @@
         <v>369</v>
       </c>
       <c r="M330" s="15" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
     </row>
     <row r="331" spans="1:13" ht="12.75" customHeight="1">
       <c r="A331" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B331" s="5" t="s">
-        <v>372</v>
+      <c r="B331" s="4" t="s">
+        <v>442</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>9</v>
@@ -13019,43 +13026,49 @@
     </row>
     <row r="332" spans="1:13" ht="12.75" customHeight="1">
       <c r="A332" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C332" s="15" t="s">
-        <v>244</v>
+        <v>372</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D332" s="5"/>
       <c r="E332" s="5"/>
       <c r="F332" s="5"/>
       <c r="G332" s="10">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="H332" s="10">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="I332" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J332" s="10"/>
-      <c r="K332" s="10"/>
+        <v>13000</v>
+      </c>
+      <c r="J332" s="10">
+        <v>25000</v>
+      </c>
+      <c r="K332" s="10">
+        <v>28000</v>
+      </c>
       <c r="L332" s="15" t="s">
         <v>369</v>
       </c>
       <c r="M332" s="15" t="s">
-        <v>387</v>
+        <v>295</v>
       </c>
     </row>
     <row r="333" spans="1:13" ht="12.75" customHeight="1">
       <c r="A333" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B333" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C333" s="15"/>
+      <c r="B333" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C333" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
       <c r="F333" s="5"/>
@@ -13082,29 +13095,23 @@
         <v>373</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="C334" s="15" t="s">
-        <v>244</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="C334" s="15"/>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
       <c r="F334" s="5"/>
       <c r="G334" s="10">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H334" s="10">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="I334" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J334" s="10">
-        <v>28000</v>
-      </c>
-      <c r="K334" s="10">
-        <v>31000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="J334" s="10"/>
+      <c r="K334" s="10"/>
       <c r="L334" s="15" t="s">
         <v>369</v>
       </c>
@@ -13117,9 +13124,11 @@
         <v>373</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C335" s="15"/>
+        <v>388</v>
+      </c>
+      <c r="C335" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
       <c r="F335" s="5"/>
@@ -13146,30 +13155,42 @@
       </c>
     </row>
     <row r="336" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A336" s="16"/>
-      <c r="B336" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C336" s="15" t="s">
-        <v>244</v>
-      </c>
+      <c r="A336" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C336" s="15"/>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
       <c r="F336" s="5"/>
-      <c r="G336" s="10"/>
-      <c r="H336" s="10"/>
-      <c r="I336" s="10"/>
-      <c r="J336" s="10"/>
-      <c r="K336" s="10"/>
-      <c r="L336" s="16"/>
+      <c r="G336" s="10">
+        <v>13000</v>
+      </c>
+      <c r="H336" s="10">
+        <v>14000</v>
+      </c>
+      <c r="I336" s="10">
+        <v>16000</v>
+      </c>
+      <c r="J336" s="10">
+        <v>28000</v>
+      </c>
+      <c r="K336" s="10">
+        <v>31000</v>
+      </c>
+      <c r="L336" s="15" t="s">
+        <v>369</v>
+      </c>
       <c r="M336" s="15" t="s">
-        <v>295</v>
+        <v>387</v>
       </c>
     </row>
     <row r="337" spans="1:13" ht="12.75" customHeight="1">
       <c r="A337" s="16"/>
       <c r="B337" s="5" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="C337" s="15" t="s">
         <v>244</v>
@@ -13188,15 +13209,25 @@
       </c>
     </row>
     <row r="338" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B338" s="1"/>
-      <c r="D338" s="1"/>
-      <c r="E338" s="1"/>
-      <c r="F338" s="1"/>
-      <c r="G338" s="2"/>
-      <c r="H338" s="2"/>
-      <c r="I338" s="2"/>
-      <c r="J338" s="2"/>
-      <c r="K338" s="2"/>
+      <c r="A338" s="16"/>
+      <c r="B338" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C338" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="D338" s="5"/>
+      <c r="E338" s="5"/>
+      <c r="F338" s="5"/>
+      <c r="G338" s="10"/>
+      <c r="H338" s="10"/>
+      <c r="I338" s="10"/>
+      <c r="J338" s="10"/>
+      <c r="K338" s="10"/>
+      <c r="L338" s="16"/>
+      <c r="M338" s="15" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="339" spans="1:13" ht="12.75" customHeight="1">
       <c r="B339" s="1"/>
@@ -22449,9 +22480,20 @@
       <c r="J1179" s="2"/>
       <c r="K1179" s="2"/>
     </row>
+    <row r="1180" spans="2:11" ht="12.75" customHeight="1">
+      <c r="B1180" s="1"/>
+      <c r="D1180" s="1"/>
+      <c r="E1180" s="1"/>
+      <c r="F1180" s="1"/>
+      <c r="G1180" s="2"/>
+      <c r="H1180" s="2"/>
+      <c r="I1180" s="2"/>
+      <c r="J1180" s="2"/>
+      <c r="K1180" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M328">
-    <sortCondition ref="B251:B328"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M329">
+    <sortCondition ref="B252:B329"/>
   </sortState>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>

--- a/chair_all.xlsx
+++ b/chair_all.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af69c26be6256a92/work/会社アプリ関連/チェア修理アプリ用/修理アプリファイル/githubアップロードセット/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{367F8678-3549-4968-BC24-5D2798A0E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{521F14BE-DE79-4C6D-A898-2CCF7453A836}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="13_ncr:1_{367F8678-3549-4968-BC24-5D2798A0E078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{487489A5-BBF3-473C-83D6-F0A26B693B4E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="562">
   <si>
     <t>シリーズ</t>
   </si>
@@ -2026,6 +2026,10 @@
     <rPh sb="3" eb="7">
       <t>キカンゲンテイ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MC10</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -2381,7 +2385,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1180"/>
+  <dimension ref="A1:M1181"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.77734375" customWidth="1"/>
@@ -9240,48 +9244,36 @@
     </row>
     <row r="214" spans="1:13" ht="12.75" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B214" s="4" t="s">
-        <v>211</v>
+        <v>560</v>
+      </c>
+      <c r="B214" s="9" t="s">
+        <v>561</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D214" s="5">
-        <v>99</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="D214" s="5"/>
       <c r="E214" s="5"/>
       <c r="F214" s="5"/>
-      <c r="G214" s="10">
-        <v>0</v>
-      </c>
-      <c r="H214" s="10">
-        <v>0</v>
-      </c>
-      <c r="I214" s="10">
-        <v>0</v>
-      </c>
-      <c r="J214" s="10">
-        <v>0</v>
-      </c>
-      <c r="K214" s="10">
-        <v>0</v>
-      </c>
+      <c r="G214" s="10"/>
+      <c r="H214" s="10"/>
+      <c r="I214" s="10"/>
+      <c r="J214" s="10"/>
+      <c r="K214" s="10"/>
       <c r="L214" s="3"/>
       <c r="M214" s="3" t="s">
-        <v>295</v>
+        <v>559</v>
       </c>
     </row>
     <row r="215" spans="1:13" ht="12.75" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B215" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B215" s="4" t="s">
         <v>211</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>9</v>
+        <v>209</v>
       </c>
       <c r="D215" s="5">
         <v>99</v>
@@ -9305,52 +9297,50 @@
       </c>
       <c r="L215" s="3"/>
       <c r="M215" s="3" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
     </row>
     <row r="216" spans="1:13" ht="12.75" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B216" s="4" t="s">
-        <v>104</v>
+        <v>210</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D216" s="5" t="s">
-        <v>84</v>
+      <c r="D216" s="5">
+        <v>99</v>
       </c>
       <c r="E216" s="5"/>
       <c r="F216" s="5"/>
       <c r="G216" s="10">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="H216" s="10">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="I216" s="10">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="J216" s="10">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="K216" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L216" s="3" t="s">
-        <v>85</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L216" s="3"/>
       <c r="M216" s="3" t="s">
-        <v>263</v>
+        <v>209</v>
       </c>
     </row>
     <row r="217" spans="1:13" ht="12.75" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B217" s="5" t="s">
-        <v>375</v>
+        <v>103</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>9</v>
@@ -9379,7 +9369,7 @@
         <v>85</v>
       </c>
       <c r="M217" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="218" spans="1:13" ht="12.75" customHeight="1">
@@ -9387,7 +9377,7 @@
         <v>123</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>9</v>
@@ -9416,76 +9406,78 @@
         <v>85</v>
       </c>
       <c r="M218" s="3" t="s">
-        <v>389</v>
+        <v>284</v>
       </c>
     </row>
     <row r="219" spans="1:13" ht="12.75" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B219" s="4" t="s">
-        <v>30</v>
+        <v>123</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E219" s="5"/>
       <c r="F219" s="5"/>
       <c r="G219" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H219" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I219" s="10">
         <v>18000</v>
       </c>
-      <c r="H219" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I219" s="10">
-        <v>24000</v>
-      </c>
       <c r="J219" s="10">
-        <v>38000</v>
+        <v>30000</v>
       </c>
       <c r="K219" s="10">
-        <v>42000</v>
+        <v>33000</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M219" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="M219" s="3" t="s">
+        <v>389</v>
+      </c>
     </row>
     <row r="220" spans="1:13" ht="12.75" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="E220" s="5"/>
       <c r="F220" s="5"/>
       <c r="G220" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H220" s="10">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I220" s="10">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J220" s="10">
-        <v>30000</v>
+        <v>38000</v>
       </c>
       <c r="K220" s="10">
-        <v>33000</v>
+        <v>42000</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="M220" s="3"/>
     </row>
@@ -9494,7 +9486,7 @@
         <v>105</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>309</v>
+        <v>106</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>9</v>
@@ -9526,35 +9518,37 @@
     </row>
     <row r="222" spans="1:13" ht="12.75" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>167</v>
+        <v>105</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>309</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D222" s="5">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E222" s="5"/>
       <c r="F222" s="5"/>
       <c r="G222" s="10">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="H222" s="10">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="I222" s="10">
-        <v>31000</v>
+        <v>18000</v>
       </c>
       <c r="J222" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K222" s="10">
-        <v>0</v>
-      </c>
-      <c r="L222" s="3"/>
+        <v>33000</v>
+      </c>
+      <c r="L222" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M222" s="3"/>
     </row>
     <row r="223" spans="1:13" ht="12.75" customHeight="1">
@@ -9562,7 +9556,7 @@
         <v>29</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>163</v>
@@ -9573,16 +9567,16 @@
       <c r="E223" s="5"/>
       <c r="F223" s="5"/>
       <c r="G223" s="10">
+        <v>24000</v>
+      </c>
+      <c r="H223" s="10">
         <v>26000</v>
       </c>
-      <c r="H223" s="10">
-        <v>28000</v>
-      </c>
       <c r="I223" s="10">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="J223" s="10">
-        <v>82000</v>
+        <v>80000</v>
       </c>
       <c r="K223" s="10">
         <v>0</v>
@@ -9592,13 +9586,13 @@
     </row>
     <row r="224" spans="1:13" ht="12.75" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>9</v>
+        <v>163</v>
       </c>
       <c r="D224" s="5">
         <v>0</v>
@@ -9606,13 +9600,13 @@
       <c r="E224" s="5"/>
       <c r="F224" s="5"/>
       <c r="G224" s="10">
+        <v>26000</v>
+      </c>
+      <c r="H224" s="10">
         <v>28000</v>
       </c>
-      <c r="H224" s="10">
-        <v>29000</v>
-      </c>
       <c r="I224" s="10">
-        <v>34000</v>
+        <v>33000</v>
       </c>
       <c r="J224" s="10">
         <v>82000</v>
@@ -9628,7 +9622,7 @@
         <v>105</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>9</v>
@@ -9639,16 +9633,16 @@
       <c r="E225" s="5"/>
       <c r="F225" s="5"/>
       <c r="G225" s="10">
-        <v>31000</v>
+        <v>28000</v>
       </c>
       <c r="H225" s="10">
-        <v>32000</v>
+        <v>29000</v>
       </c>
       <c r="I225" s="10">
-        <v>37000</v>
+        <v>34000</v>
       </c>
       <c r="J225" s="10">
-        <v>85000</v>
+        <v>82000</v>
       </c>
       <c r="K225" s="10">
         <v>0</v>
@@ -9661,7 +9655,7 @@
         <v>105</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>9</v>
@@ -9672,16 +9666,16 @@
       <c r="E226" s="5"/>
       <c r="F226" s="5"/>
       <c r="G226" s="10">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="H226" s="10">
-        <v>34000</v>
+        <v>32000</v>
       </c>
       <c r="I226" s="10">
-        <v>39000</v>
+        <v>37000</v>
       </c>
       <c r="J226" s="10">
-        <v>87000</v>
+        <v>85000</v>
       </c>
       <c r="K226" s="10">
         <v>0</v>
@@ -9691,47 +9685,43 @@
     </row>
     <row r="227" spans="1:13" ht="12.75" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B227" s="4" t="s">
-        <v>32</v>
+        <v>105</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>171</v>
       </c>
       <c r="C227" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D227" s="5" t="s">
-        <v>10</v>
+      <c r="D227" s="5">
+        <v>0</v>
       </c>
       <c r="E227" s="5"/>
       <c r="F227" s="5"/>
       <c r="G227" s="10">
-        <v>18000</v>
+        <v>33000</v>
       </c>
       <c r="H227" s="10">
-        <v>20000</v>
+        <v>34000</v>
       </c>
       <c r="I227" s="10">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="J227" s="10">
-        <v>38000</v>
+        <v>87000</v>
       </c>
       <c r="K227" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L227" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M227" s="3" t="s">
-        <v>270</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L227" s="3"/>
+      <c r="M227" s="3"/>
     </row>
     <row r="228" spans="1:13" ht="12.75" customHeight="1">
       <c r="A228" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>310</v>
+        <v>32</v>
       </c>
       <c r="C228" s="3" t="s">
         <v>9</v>
@@ -9768,33 +9758,33 @@
         <v>31</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>67</v>
+        <v>310</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E229" s="5"/>
       <c r="F229" s="5"/>
       <c r="G229" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="H229" s="10">
-        <v>49000</v>
+        <v>20000</v>
       </c>
       <c r="I229" s="10">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="J229" s="10">
-        <v>80000</v>
+        <v>38000</v>
       </c>
       <c r="K229" s="10">
-        <v>90000</v>
+        <v>42000</v>
       </c>
       <c r="L229" s="3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="M229" s="3" t="s">
         <v>270</v>
@@ -9805,7 +9795,7 @@
         <v>31</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c r="C230" s="3" t="s">
         <v>43</v>
@@ -9839,36 +9829,36 @@
     </row>
     <row r="231" spans="1:13" ht="12.75" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>34</v>
+        <v>219</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="E231" s="5"/>
       <c r="F231" s="5"/>
       <c r="G231" s="10">
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="H231" s="10">
-        <v>20000</v>
+        <v>49000</v>
       </c>
       <c r="I231" s="10">
-        <v>24000</v>
+        <v>53000</v>
       </c>
       <c r="J231" s="10">
-        <v>38000</v>
+        <v>80000</v>
       </c>
       <c r="K231" s="10">
-        <v>42000</v>
+        <v>90000</v>
       </c>
       <c r="L231" s="3" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="M231" s="3" t="s">
         <v>270</v>
@@ -9876,62 +9866,62 @@
     </row>
     <row r="232" spans="1:13" ht="12.75" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>345</v>
+        <v>33</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>344</v>
+        <v>34</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D232" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E232" s="5"/>
       <c r="F232" s="5"/>
-      <c r="G232" s="10"/>
-      <c r="H232" s="10"/>
-      <c r="I232" s="10"/>
-      <c r="J232" s="10"/>
-      <c r="K232" s="10"/>
-      <c r="L232" s="3"/>
+      <c r="G232" s="10">
+        <v>18000</v>
+      </c>
+      <c r="H232" s="10">
+        <v>20000</v>
+      </c>
+      <c r="I232" s="10">
+        <v>24000</v>
+      </c>
+      <c r="J232" s="10">
+        <v>38000</v>
+      </c>
+      <c r="K232" s="10">
+        <v>42000</v>
+      </c>
+      <c r="L232" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M232" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="233" spans="1:13" ht="12.75" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>35</v>
+        <v>345</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>220</v>
+        <v>344</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D233" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D233" s="5"/>
       <c r="E233" s="5"/>
       <c r="F233" s="5"/>
-      <c r="G233" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H233" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I233" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J233" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K233" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L233" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="G233" s="10"/>
+      <c r="H233" s="10"/>
+      <c r="I233" s="10"/>
+      <c r="J233" s="10"/>
+      <c r="K233" s="10"/>
+      <c r="L233" s="3"/>
       <c r="M233" s="3" t="s">
-        <v>12</v>
+        <v>270</v>
       </c>
     </row>
     <row r="234" spans="1:13" ht="12.75" customHeight="1">
@@ -9939,7 +9929,7 @@
         <v>35</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>9</v>
@@ -9976,33 +9966,33 @@
         <v>35</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="E235" s="5"/>
       <c r="F235" s="5"/>
       <c r="G235" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="H235" s="10">
-        <v>49000</v>
+        <v>20000</v>
       </c>
       <c r="I235" s="10">
-        <v>53000</v>
+        <v>24000</v>
       </c>
       <c r="J235" s="10">
-        <v>80000</v>
+        <v>38000</v>
       </c>
       <c r="K235" s="10">
-        <v>90000</v>
+        <v>42000</v>
       </c>
       <c r="L235" s="3" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="M235" s="3" t="s">
         <v>12</v>
@@ -10013,7 +10003,7 @@
         <v>35</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>311</v>
+        <v>68</v>
       </c>
       <c r="C236" s="3" t="s">
         <v>43</v>
@@ -10047,25 +10037,39 @@
     </row>
     <row r="237" spans="1:13" ht="12.75" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>319</v>
+        <v>35</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D237" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D237" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E237" s="5"/>
       <c r="F237" s="5"/>
-      <c r="G237" s="10"/>
-      <c r="H237" s="10"/>
-      <c r="I237" s="10"/>
-      <c r="J237" s="10"/>
-      <c r="K237" s="10"/>
-      <c r="L237" s="3"/>
+      <c r="G237" s="10">
+        <v>45000</v>
+      </c>
+      <c r="H237" s="10">
+        <v>49000</v>
+      </c>
+      <c r="I237" s="10">
+        <v>53000</v>
+      </c>
+      <c r="J237" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K237" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L237" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="M237" s="3" t="s">
-        <v>295</v>
+        <v>12</v>
       </c>
     </row>
     <row r="238" spans="1:13" ht="12.75" customHeight="1">
@@ -10073,7 +10077,7 @@
         <v>319</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>233</v>
@@ -10096,7 +10100,7 @@
         <v>319</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>417</v>
+        <v>321</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>233</v>
@@ -10119,7 +10123,7 @@
         <v>319</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>322</v>
+        <v>417</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>233</v>
@@ -10139,10 +10143,10 @@
     </row>
     <row r="241" spans="1:13" ht="12.75" customHeight="1">
       <c r="A241" s="3" t="s">
-        <v>418</v>
+        <v>319</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>419</v>
+        <v>322</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>233</v>
@@ -10157,15 +10161,15 @@
       <c r="K241" s="10"/>
       <c r="L241" s="3"/>
       <c r="M241" s="3" t="s">
-        <v>420</v>
+        <v>295</v>
       </c>
     </row>
     <row r="242" spans="1:13" ht="12.75" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>323</v>
+        <v>418</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>313</v>
+        <v>419</v>
       </c>
       <c r="C242" s="3" t="s">
         <v>233</v>
@@ -10180,7 +10184,7 @@
       <c r="K242" s="10"/>
       <c r="L242" s="3"/>
       <c r="M242" s="3" t="s">
-        <v>324</v>
+        <v>420</v>
       </c>
     </row>
     <row r="243" spans="1:13" ht="12.75" customHeight="1">
@@ -10188,7 +10192,7 @@
         <v>323</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>233</v>
@@ -10211,7 +10215,7 @@
         <v>323</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>233</v>
@@ -10231,47 +10235,33 @@
     </row>
     <row r="245" spans="1:13" ht="12.75" customHeight="1">
       <c r="A245" s="3" t="s">
-        <v>107</v>
+        <v>323</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D245" s="5"/>
       <c r="E245" s="5"/>
       <c r="F245" s="5"/>
-      <c r="G245" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H245" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I245" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J245" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K245" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L245" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G245" s="10"/>
+      <c r="H245" s="10"/>
+      <c r="I245" s="10"/>
+      <c r="J245" s="10"/>
+      <c r="K245" s="10"/>
+      <c r="L245" s="3"/>
       <c r="M245" s="3" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
     </row>
     <row r="246" spans="1:13" ht="12.75" customHeight="1">
       <c r="A246" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B246" s="5" t="s">
-        <v>250</v>
+      <c r="B246" s="4" t="s">
+        <v>251</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>9</v>
@@ -10308,20 +10298,34 @@
         <v>107</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>326</v>
+        <v>250</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D247" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E247" s="5"/>
       <c r="F247" s="5"/>
-      <c r="G247" s="10"/>
-      <c r="H247" s="10"/>
-      <c r="I247" s="10"/>
-      <c r="J247" s="10"/>
-      <c r="K247" s="10"/>
-      <c r="L247" s="3"/>
+      <c r="G247" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H247" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I247" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J247" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K247" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L247" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M247" s="3" t="s">
         <v>295</v>
       </c>
@@ -10331,7 +10335,7 @@
         <v>107</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>421</v>
+        <v>326</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>233</v>
@@ -10354,34 +10358,20 @@
         <v>107</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>252</v>
+        <v>421</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D249" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D249" s="5"/>
       <c r="E249" s="5"/>
       <c r="F249" s="5"/>
-      <c r="G249" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H249" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I249" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J249" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K249" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L249" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G249" s="10"/>
+      <c r="H249" s="10"/>
+      <c r="I249" s="10"/>
+      <c r="J249" s="10"/>
+      <c r="K249" s="10"/>
+      <c r="L249" s="3"/>
       <c r="M249" s="3" t="s">
         <v>295</v>
       </c>
@@ -10391,7 +10381,7 @@
         <v>107</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>437</v>
+        <v>252</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>9</v>
@@ -10424,69 +10414,69 @@
       </c>
     </row>
     <row r="251" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A251" s="3"/>
+      <c r="A251" s="3" t="s">
+        <v>107</v>
+      </c>
       <c r="B251" s="5" t="s">
-        <v>327</v>
+        <v>437</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D251" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E251" s="5"/>
       <c r="F251" s="5"/>
-      <c r="G251" s="10"/>
-      <c r="H251" s="10"/>
-      <c r="I251" s="10"/>
-      <c r="J251" s="10"/>
-      <c r="K251" s="10"/>
-      <c r="L251" s="3"/>
+      <c r="G251" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H251" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I251" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J251" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K251" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L251" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M251" s="3" t="s">
-        <v>328</v>
+        <v>295</v>
       </c>
     </row>
     <row r="252" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A252" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="A252" s="3"/>
       <c r="B252" s="5" t="s">
-        <v>120</v>
+        <v>327</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D252" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D252" s="5"/>
       <c r="E252" s="5"/>
       <c r="F252" s="5"/>
-      <c r="G252" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H252" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I252" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J252" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K252" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L252" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G252" s="10"/>
+      <c r="H252" s="10"/>
+      <c r="I252" s="10"/>
+      <c r="J252" s="10"/>
+      <c r="K252" s="10"/>
+      <c r="L252" s="3"/>
       <c r="M252" s="3" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="253" spans="1:13" ht="12.75" customHeight="1">
       <c r="A253" s="3" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>9</v>
@@ -10523,40 +10513,44 @@
         <v>126</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D254" s="5">
-        <v>0</v>
+      <c r="D254" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E254" s="5"/>
       <c r="F254" s="5"/>
       <c r="G254" s="10">
-        <v>37000</v>
+        <v>15000</v>
       </c>
       <c r="H254" s="10">
-        <v>39000</v>
+        <v>16000</v>
       </c>
       <c r="I254" s="10">
-        <v>45000</v>
+        <v>18000</v>
       </c>
       <c r="J254" s="10">
-        <v>99000</v>
+        <v>30000</v>
       </c>
       <c r="K254" s="10">
-        <v>0</v>
-      </c>
-      <c r="L254" s="3"/>
-      <c r="M254" s="3"/>
+        <v>33000</v>
+      </c>
+      <c r="L254" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M254" s="3" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="255" spans="1:13" ht="12.75" customHeight="1">
       <c r="A255" s="3" t="s">
         <v>126</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>9</v>
@@ -10567,16 +10561,16 @@
       <c r="E255" s="5"/>
       <c r="F255" s="5"/>
       <c r="G255" s="10">
-        <v>40000</v>
+        <v>37000</v>
       </c>
       <c r="H255" s="10">
-        <v>42000</v>
+        <v>39000</v>
       </c>
       <c r="I255" s="10">
-        <v>48000</v>
+        <v>45000</v>
       </c>
       <c r="J255" s="10">
-        <v>102000</v>
+        <v>99000</v>
       </c>
       <c r="K255" s="10">
         <v>0</v>
@@ -10586,47 +10580,43 @@
     </row>
     <row r="256" spans="1:13" ht="12.75" customHeight="1">
       <c r="A256" s="3" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D256" s="5" t="s">
-        <v>84</v>
+      <c r="D256" s="5">
+        <v>0</v>
       </c>
       <c r="E256" s="5"/>
       <c r="F256" s="5"/>
       <c r="G256" s="10">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="H256" s="10">
-        <v>16000</v>
+        <v>42000</v>
       </c>
       <c r="I256" s="10">
-        <v>18000</v>
+        <v>48000</v>
       </c>
       <c r="J256" s="10">
-        <v>30000</v>
+        <v>102000</v>
       </c>
       <c r="K256" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L256" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M256" s="3" t="s">
-        <v>295</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L256" s="3"/>
+      <c r="M256" s="3"/>
     </row>
     <row r="257" spans="1:13" ht="12.75" customHeight="1">
       <c r="A257" s="3" t="s">
         <v>108</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>9</v>
@@ -10660,10 +10650,10 @@
     </row>
     <row r="258" spans="1:13" ht="12.75" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B258" s="11" t="s">
-        <v>460</v>
+        <v>108</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>9</v>
@@ -10692,15 +10682,15 @@
         <v>85</v>
       </c>
       <c r="M258" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="259" spans="1:13" ht="12.75" customHeight="1">
       <c r="A259" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B259" s="5" t="s">
-        <v>110</v>
+      <c r="B259" s="11" t="s">
+        <v>460</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>9</v>
@@ -10736,8 +10726,8 @@
       <c r="A260" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="B260" s="11" t="s">
-        <v>111</v>
+      <c r="B260" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>9</v>
@@ -10771,31 +10761,47 @@
     </row>
     <row r="261" spans="1:13" ht="12.75" customHeight="1">
       <c r="A261" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B261" s="5" t="s">
-        <v>235</v>
+        <v>109</v>
+      </c>
+      <c r="B261" s="11" t="s">
+        <v>111</v>
       </c>
       <c r="C261" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D261" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
-      <c r="G261" s="10"/>
-      <c r="H261" s="10"/>
-      <c r="I261" s="10"/>
-      <c r="J261" s="10"/>
-      <c r="K261" s="10"/>
-      <c r="L261" s="3"/>
-      <c r="M261" s="3"/>
+      <c r="G261" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H261" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I261" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J261" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K261" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L261" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M261" s="3" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="262" spans="1:13" ht="12.75" customHeight="1">
       <c r="A262" s="3" t="s">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>329</v>
+        <v>235</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>175</v>
@@ -10809,16 +10815,14 @@
       <c r="J262" s="10"/>
       <c r="K262" s="10"/>
       <c r="L262" s="3"/>
-      <c r="M262" s="3" t="s">
-        <v>80</v>
-      </c>
+      <c r="M262" s="3"/>
     </row>
     <row r="263" spans="1:13" ht="12.75" customHeight="1">
       <c r="A263" s="3" t="s">
         <v>330</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>422</v>
+        <v>329</v>
       </c>
       <c r="C263" s="3" t="s">
         <v>175</v>
@@ -10838,34 +10842,22 @@
     </row>
     <row r="264" spans="1:13" ht="12.75" customHeight="1">
       <c r="A264" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B264" s="4" t="s">
-        <v>213</v>
+        <v>330</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>422</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D264" s="5">
-        <v>99</v>
-      </c>
+      <c r="D264" s="5"/>
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
-      <c r="G264" s="10">
-        <v>0</v>
-      </c>
-      <c r="H264" s="10">
-        <v>0</v>
-      </c>
-      <c r="I264" s="10">
-        <v>0</v>
-      </c>
-      <c r="J264" s="10">
-        <v>0</v>
-      </c>
-      <c r="K264" s="10">
-        <v>0</v>
-      </c>
+      <c r="G264" s="10"/>
+      <c r="H264" s="10"/>
+      <c r="I264" s="10"/>
+      <c r="J264" s="10"/>
+      <c r="K264" s="10"/>
       <c r="L264" s="3"/>
       <c r="M264" s="3" t="s">
         <v>80</v>
@@ -10873,10 +10865,10 @@
     </row>
     <row r="265" spans="1:13" ht="12.75" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>175</v>
@@ -10908,22 +10900,34 @@
     </row>
     <row r="266" spans="1:13" ht="12.75" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="C266" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D266" s="5"/>
+      <c r="D266" s="5">
+        <v>99</v>
+      </c>
       <c r="E266" s="5"/>
       <c r="F266" s="5"/>
-      <c r="G266" s="10"/>
-      <c r="H266" s="10"/>
-      <c r="I266" s="10"/>
-      <c r="J266" s="10"/>
-      <c r="K266" s="10"/>
+      <c r="G266" s="10">
+        <v>0</v>
+      </c>
+      <c r="H266" s="10">
+        <v>0</v>
+      </c>
+      <c r="I266" s="10">
+        <v>0</v>
+      </c>
+      <c r="J266" s="10">
+        <v>0</v>
+      </c>
+      <c r="K266" s="10">
+        <v>0</v>
+      </c>
       <c r="L266" s="3"/>
       <c r="M266" s="3" t="s">
         <v>80</v>
@@ -10934,7 +10938,7 @@
         <v>237</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C267" s="3" t="s">
         <v>175</v>
@@ -10954,10 +10958,10 @@
     </row>
     <row r="268" spans="1:13" ht="12.75" customHeight="1">
       <c r="A268" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>175</v>
@@ -10972,44 +10976,30 @@
       <c r="K268" s="10"/>
       <c r="L268" s="3"/>
       <c r="M268" s="3" t="s">
-        <v>263</v>
+        <v>80</v>
       </c>
     </row>
     <row r="269" spans="1:13" ht="12.75" customHeight="1">
       <c r="A269" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B269" s="5" t="s">
-        <v>394</v>
+        <v>240</v>
+      </c>
+      <c r="B269" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="C269" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D269" s="5" t="s">
-        <v>148</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="D269" s="5"/>
       <c r="E269" s="5"/>
       <c r="F269" s="5"/>
-      <c r="G269" s="10">
-        <v>26000</v>
-      </c>
-      <c r="H269" s="10">
-        <v>30000</v>
-      </c>
-      <c r="I269" s="10">
-        <v>34000</v>
-      </c>
-      <c r="J269" s="10">
-        <v>0</v>
-      </c>
-      <c r="K269" s="10">
-        <v>0</v>
-      </c>
-      <c r="L269" s="3" t="s">
-        <v>149</v>
-      </c>
+      <c r="G269" s="10"/>
+      <c r="H269" s="10"/>
+      <c r="I269" s="10"/>
+      <c r="J269" s="10"/>
+      <c r="K269" s="10"/>
+      <c r="L269" s="3"/>
       <c r="M269" s="3" t="s">
-        <v>395</v>
+        <v>263</v>
       </c>
     </row>
     <row r="270" spans="1:13" ht="12.75" customHeight="1">
@@ -11017,7 +11007,7 @@
         <v>147</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>43</v>
@@ -11051,25 +11041,39 @@
     </row>
     <row r="271" spans="1:13" ht="12.75" customHeight="1">
       <c r="A271" s="3" t="s">
-        <v>69</v>
+        <v>147</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>331</v>
+        <v>396</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D271" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D271" s="5" t="s">
+        <v>148</v>
+      </c>
       <c r="E271" s="5"/>
       <c r="F271" s="5"/>
-      <c r="G271" s="10"/>
-      <c r="H271" s="10"/>
-      <c r="I271" s="10"/>
-      <c r="J271" s="10"/>
-      <c r="K271" s="10"/>
-      <c r="L271" s="3"/>
+      <c r="G271" s="10">
+        <v>26000</v>
+      </c>
+      <c r="H271" s="10">
+        <v>30000</v>
+      </c>
+      <c r="I271" s="10">
+        <v>34000</v>
+      </c>
+      <c r="J271" s="10">
+        <v>0</v>
+      </c>
+      <c r="K271" s="10">
+        <v>0</v>
+      </c>
+      <c r="L271" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="M271" s="3" t="s">
-        <v>270</v>
+        <v>395</v>
       </c>
     </row>
     <row r="272" spans="1:13" ht="12.75" customHeight="1">
@@ -11077,34 +11081,20 @@
         <v>69</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>256</v>
+        <v>331</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D272" s="5" t="s">
-        <v>46</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D272" s="5"/>
       <c r="E272" s="5"/>
       <c r="F272" s="5"/>
-      <c r="G272" s="10">
-        <v>45000</v>
-      </c>
-      <c r="H272" s="10">
-        <v>49000</v>
-      </c>
-      <c r="I272" s="10">
-        <v>53000</v>
-      </c>
-      <c r="J272" s="10">
-        <v>80000</v>
-      </c>
-      <c r="K272" s="10">
-        <v>90000</v>
-      </c>
-      <c r="L272" s="3" t="s">
-        <v>47</v>
-      </c>
+      <c r="G272" s="10"/>
+      <c r="H272" s="10"/>
+      <c r="I272" s="10"/>
+      <c r="J272" s="10"/>
+      <c r="K272" s="10"/>
+      <c r="L272" s="3"/>
       <c r="M272" s="3" t="s">
         <v>270</v>
       </c>
@@ -11114,7 +11104,7 @@
         <v>69</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C273" s="3" t="s">
         <v>43</v>
@@ -11151,57 +11141,59 @@
         <v>69</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>332</v>
+        <v>255</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D274" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E274" s="5"/>
       <c r="F274" s="5"/>
-      <c r="G274" s="10"/>
-      <c r="H274" s="10"/>
-      <c r="I274" s="10"/>
-      <c r="J274" s="10"/>
-      <c r="K274" s="10"/>
-      <c r="L274" s="3"/>
+      <c r="G274" s="10">
+        <v>45000</v>
+      </c>
+      <c r="H274" s="10">
+        <v>49000</v>
+      </c>
+      <c r="I274" s="10">
+        <v>53000</v>
+      </c>
+      <c r="J274" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K274" s="10">
+        <v>90000</v>
+      </c>
+      <c r="L274" s="3" t="s">
+        <v>47</v>
+      </c>
       <c r="M274" s="3" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="275" spans="1:13" ht="12.75" customHeight="1">
       <c r="A275" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>398</v>
+        <v>332</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="D275" s="5"/>
       <c r="E275" s="5"/>
       <c r="F275" s="5"/>
-      <c r="G275" s="10">
-        <v>42000</v>
-      </c>
-      <c r="H275" s="10">
-        <v>46000</v>
-      </c>
-      <c r="I275" s="10">
-        <v>50000</v>
-      </c>
-      <c r="J275" s="10">
-        <v>77000</v>
-      </c>
-      <c r="K275" s="10">
-        <v>87000</v>
-      </c>
-      <c r="L275" s="3" t="s">
-        <v>397</v>
-      </c>
+      <c r="G275" s="10"/>
+      <c r="H275" s="10"/>
+      <c r="I275" s="10"/>
+      <c r="J275" s="10"/>
+      <c r="K275" s="10"/>
+      <c r="L275" s="3"/>
       <c r="M275" s="3" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
     </row>
     <row r="276" spans="1:13" ht="12.75" customHeight="1">
@@ -11209,7 +11201,7 @@
         <v>70</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>455</v>
+        <v>398</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>43</v>
@@ -11244,34 +11236,34 @@
         <v>70</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>361</v>
+        <v>455</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>244</v>
+        <v>43</v>
       </c>
       <c r="D277" s="5"/>
       <c r="E277" s="5"/>
       <c r="F277" s="5"/>
       <c r="G277" s="10">
-        <v>15000</v>
+        <v>42000</v>
       </c>
       <c r="H277" s="10">
-        <v>16000</v>
+        <v>46000</v>
       </c>
       <c r="I277" s="10">
-        <v>18000</v>
+        <v>50000</v>
       </c>
       <c r="J277" s="10">
-        <v>30000</v>
+        <v>77000</v>
       </c>
       <c r="K277" s="10">
-        <v>33000</v>
+        <v>87000</v>
       </c>
       <c r="L277" s="3" t="s">
-        <v>85</v>
+        <v>397</v>
       </c>
       <c r="M277" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="12.75" customHeight="1">
@@ -11279,14 +11271,12 @@
         <v>70</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>438</v>
+        <v>361</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D278" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D278" s="5"/>
       <c r="E278" s="5"/>
       <c r="F278" s="5"/>
       <c r="G278" s="10">
@@ -11316,10 +11306,10 @@
         <v>70</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>362</v>
+        <v>438</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D279" s="5" t="s">
         <v>84</v>
@@ -11327,22 +11317,22 @@
       <c r="E279" s="5"/>
       <c r="F279" s="5"/>
       <c r="G279" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H279" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I279" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J279" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K279" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L279" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="M279" s="3" t="s">
         <v>270</v>
@@ -11353,13 +11343,13 @@
         <v>70</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>439</v>
+        <v>362</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E280" s="5"/>
       <c r="F280" s="5"/>
@@ -11390,30 +11380,36 @@
         <v>70</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>382</v>
+        <v>439</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D281" s="5"/>
+        <v>43</v>
+      </c>
+      <c r="D281" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="E281" s="5"/>
       <c r="F281" s="5"/>
       <c r="G281" s="10">
-        <v>13000</v>
+        <v>45000</v>
       </c>
       <c r="H281" s="10">
-        <v>14000</v>
+        <v>49000</v>
       </c>
       <c r="I281" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J281" s="10"/>
-      <c r="K281" s="10"/>
+        <v>53000</v>
+      </c>
+      <c r="J281" s="10">
+        <v>80000</v>
+      </c>
+      <c r="K281" s="10">
+        <v>90000</v>
+      </c>
       <c r="L281" s="3" t="s">
-        <v>384</v>
+        <v>47</v>
       </c>
       <c r="M281" s="3" t="s">
-        <v>383</v>
+        <v>270</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="12.75" customHeight="1">
@@ -11421,7 +11417,7 @@
         <v>70</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>440</v>
+        <v>382</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>244</v>
@@ -11452,34 +11448,30 @@
         <v>70</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>399</v>
+        <v>440</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>43</v>
+        <v>244</v>
       </c>
       <c r="D283" s="5"/>
       <c r="E283" s="5"/>
       <c r="F283" s="5"/>
       <c r="G283" s="10">
-        <v>38000</v>
+        <v>13000</v>
       </c>
       <c r="H283" s="10">
-        <v>42000</v>
+        <v>14000</v>
       </c>
       <c r="I283" s="10">
-        <v>46000</v>
-      </c>
-      <c r="J283" s="10">
-        <v>73000</v>
-      </c>
-      <c r="K283" s="10">
-        <v>83000</v>
-      </c>
+        <v>16000</v>
+      </c>
+      <c r="J283" s="10"/>
+      <c r="K283" s="10"/>
       <c r="L283" s="3" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="M283" s="3" t="s">
-        <v>295</v>
+        <v>383</v>
       </c>
     </row>
     <row r="284" spans="1:13" ht="12.75" customHeight="1">
@@ -11487,7 +11479,7 @@
         <v>70</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>456</v>
+        <v>399</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>43</v>
@@ -11519,94 +11511,94 @@
     </row>
     <row r="285" spans="1:13" ht="12.75" customHeight="1">
       <c r="A285" s="3" t="s">
-        <v>339</v>
+        <v>70</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>233</v>
+        <v>43</v>
       </c>
       <c r="D285" s="5"/>
       <c r="E285" s="5"/>
       <c r="F285" s="5"/>
-      <c r="G285" s="10"/>
-      <c r="H285" s="10"/>
-      <c r="I285" s="10"/>
-      <c r="J285" s="10"/>
-      <c r="K285" s="10"/>
-      <c r="L285" s="3"/>
+      <c r="G285" s="10">
+        <v>38000</v>
+      </c>
+      <c r="H285" s="10">
+        <v>42000</v>
+      </c>
+      <c r="I285" s="10">
+        <v>46000</v>
+      </c>
+      <c r="J285" s="10">
+        <v>73000</v>
+      </c>
+      <c r="K285" s="10">
+        <v>83000</v>
+      </c>
+      <c r="L285" s="3" t="s">
+        <v>397</v>
+      </c>
       <c r="M285" s="3" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
     </row>
     <row r="286" spans="1:13" ht="12.75" customHeight="1">
       <c r="A286" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B286" s="4" t="s">
-        <v>37</v>
+        <v>339</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D286" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D286" s="5"/>
       <c r="E286" s="5"/>
       <c r="F286" s="5"/>
-      <c r="G286" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H286" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I286" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J286" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K286" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L286" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="G286" s="10"/>
+      <c r="H286" s="10"/>
+      <c r="I286" s="10"/>
+      <c r="J286" s="10"/>
+      <c r="K286" s="10"/>
+      <c r="L286" s="3"/>
       <c r="M286" s="3" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
     </row>
     <row r="287" spans="1:13" ht="12.75" customHeight="1">
       <c r="A287" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B287" s="9" t="s">
-        <v>467</v>
+      <c r="B287" s="4" t="s">
+        <v>37</v>
       </c>
       <c r="C287" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D287" s="5"/>
+      <c r="D287" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E287" s="5"/>
       <c r="F287" s="5"/>
       <c r="G287" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H287" s="10">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="I287" s="10">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="J287" s="10">
-        <v>35000</v>
+        <v>38000</v>
       </c>
       <c r="K287" s="10">
-        <v>39000</v>
+        <v>42000</v>
       </c>
       <c r="L287" s="3" t="s">
-        <v>363</v>
+        <v>11</v>
       </c>
       <c r="M287" s="3" t="s">
         <v>295</v>
@@ -11616,8 +11608,8 @@
       <c r="A288" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B288" s="4" t="s">
-        <v>364</v>
+      <c r="B288" s="9" t="s">
+        <v>467</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>9</v>
@@ -11626,68 +11618,66 @@
       <c r="E288" s="5"/>
       <c r="F288" s="5"/>
       <c r="G288" s="10">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H288" s="10">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="I288" s="10">
-        <v>16000</v>
+        <v>21000</v>
       </c>
       <c r="J288" s="10">
-        <v>28000</v>
+        <v>35000</v>
       </c>
       <c r="K288" s="10">
-        <v>31000</v>
-      </c>
-      <c r="L288" s="3"/>
+        <v>39000</v>
+      </c>
+      <c r="L288" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="M288" s="3" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="289" spans="1:13" ht="12.75" customHeight="1">
       <c r="A289" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>241</v>
+        <v>364</v>
       </c>
       <c r="C289" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D289" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="D289" s="5"/>
       <c r="E289" s="5"/>
       <c r="F289" s="5"/>
       <c r="G289" s="10">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H289" s="10">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="I289" s="10">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="J289" s="10">
-        <v>38000</v>
+        <v>28000</v>
       </c>
       <c r="K289" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L289" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>31000</v>
+      </c>
+      <c r="L289" s="3"/>
       <c r="M289" s="3" t="s">
-        <v>270</v>
+        <v>295</v>
       </c>
     </row>
     <row r="290" spans="1:13" ht="12.75" customHeight="1">
       <c r="A290" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B290" s="11" t="s">
-        <v>242</v>
+      <c r="B290" s="4" t="s">
+        <v>241</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>9</v>
@@ -11721,39 +11711,39 @@
     </row>
     <row r="291" spans="1:13" ht="12.75" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C291" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>84</v>
+        <v>10</v>
       </c>
       <c r="E291" s="5"/>
       <c r="F291" s="5"/>
       <c r="G291" s="10">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H291" s="10">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I291" s="10">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="J291" s="10">
-        <v>30000</v>
+        <v>38000</v>
       </c>
       <c r="K291" s="10">
-        <v>33000</v>
+        <v>42000</v>
       </c>
       <c r="L291" s="3" t="s">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="M291" s="3" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="292" spans="1:13" ht="12.75" customHeight="1">
@@ -11761,7 +11751,7 @@
         <v>112</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>9</v>
@@ -11795,45 +11785,47 @@
     </row>
     <row r="293" spans="1:13" ht="12.75" customHeight="1">
       <c r="A293" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B293" s="5" t="s">
-        <v>72</v>
+        <v>112</v>
+      </c>
+      <c r="B293" s="11" t="s">
+        <v>258</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E293" s="5"/>
       <c r="F293" s="5"/>
       <c r="G293" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H293" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I293" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J293" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K293" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L293" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="M293" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="M293" s="3" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="294" spans="1:13" ht="12.75" customHeight="1">
       <c r="A294" s="3" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>401</v>
+        <v>72</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>43</v>
@@ -11868,7 +11860,7 @@
         <v>71</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C295" s="3" t="s">
         <v>43</v>
@@ -11900,36 +11892,36 @@
     </row>
     <row r="296" spans="1:13" ht="12.75" customHeight="1">
       <c r="A296" s="3" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>81</v>
+        <v>400</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>43</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E296" s="5"/>
       <c r="F296" s="5"/>
       <c r="G296" s="10">
-        <v>32000</v>
+        <v>45000</v>
       </c>
       <c r="H296" s="10">
-        <v>36000</v>
+        <v>49000</v>
       </c>
       <c r="I296" s="10">
-        <v>40000</v>
+        <v>53000</v>
       </c>
       <c r="J296" s="10">
-        <v>67000</v>
+        <v>80000</v>
       </c>
       <c r="K296" s="10">
-        <v>77000</v>
+        <v>90000</v>
       </c>
       <c r="L296" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="M296" s="3"/>
     </row>
@@ -11937,34 +11929,34 @@
       <c r="A297" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B297" s="11" t="s">
-        <v>113</v>
+      <c r="B297" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E297" s="5"/>
       <c r="F297" s="5"/>
       <c r="G297" s="10">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H297" s="10">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="I297" s="10">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="J297" s="10">
-        <v>30000</v>
+        <v>67000</v>
       </c>
       <c r="K297" s="10">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="L297" s="3" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="M297" s="3"/>
     </row>
@@ -11973,33 +11965,33 @@
         <v>38</v>
       </c>
       <c r="B298" s="11" t="s">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E298" s="5"/>
       <c r="F298" s="5"/>
       <c r="G298" s="10">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="H298" s="10">
-        <v>36000</v>
+        <v>16000</v>
       </c>
       <c r="I298" s="10">
-        <v>40000</v>
+        <v>18000</v>
       </c>
       <c r="J298" s="10">
-        <v>67000</v>
+        <v>30000</v>
       </c>
       <c r="K298" s="10">
-        <v>77000</v>
+        <v>33000</v>
       </c>
       <c r="L298" s="3" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="M298" s="3"/>
     </row>
@@ -12008,59 +12000,71 @@
         <v>38</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E299" s="5"/>
       <c r="F299" s="5"/>
       <c r="G299" s="10">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H299" s="10">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="I299" s="10">
-        <v>18000</v>
+        <v>40000</v>
       </c>
       <c r="J299" s="10">
-        <v>30000</v>
+        <v>67000</v>
       </c>
       <c r="K299" s="10">
-        <v>33000</v>
+        <v>77000</v>
       </c>
       <c r="L299" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M299" s="3" t="s">
-        <v>263</v>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="M299" s="3"/>
     </row>
     <row r="300" spans="1:13" ht="12.75" customHeight="1">
       <c r="A300" s="3" t="s">
-        <v>335</v>
+        <v>38</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>336</v>
+        <v>114</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D300" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E300" s="5"/>
       <c r="F300" s="5"/>
-      <c r="G300" s="10"/>
-      <c r="H300" s="10"/>
-      <c r="I300" s="10"/>
-      <c r="J300" s="10"/>
-      <c r="K300" s="10"/>
-      <c r="L300" s="3"/>
+      <c r="G300" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H300" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I300" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J300" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K300" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L300" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M300" s="3" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="301" spans="1:13" ht="12.75" customHeight="1">
@@ -12068,7 +12072,7 @@
         <v>335</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>423</v>
+        <v>336</v>
       </c>
       <c r="C301" s="3" t="s">
         <v>233</v>
@@ -12091,7 +12095,7 @@
         <v>335</v>
       </c>
       <c r="B302" s="11" t="s">
-        <v>337</v>
+        <v>423</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>233</v>
@@ -12111,37 +12115,23 @@
     </row>
     <row r="303" spans="1:13" ht="12.75" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B303" s="5" t="s">
-        <v>115</v>
+        <v>335</v>
+      </c>
+      <c r="B303" s="11" t="s">
+        <v>337</v>
       </c>
       <c r="C303" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D303" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="D303" s="5"/>
       <c r="E303" s="5"/>
       <c r="F303" s="5"/>
-      <c r="G303" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H303" s="10">
-        <v>16000</v>
-      </c>
-      <c r="I303" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J303" s="10">
-        <v>30000</v>
-      </c>
-      <c r="K303" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L303" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="G303" s="10"/>
+      <c r="H303" s="10"/>
+      <c r="I303" s="10"/>
+      <c r="J303" s="10"/>
+      <c r="K303" s="10"/>
+      <c r="L303" s="3"/>
       <c r="M303" s="3" t="s">
         <v>284</v>
       </c>
@@ -12151,33 +12141,33 @@
         <v>73</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>402</v>
+        <v>115</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="E304" s="5"/>
       <c r="F304" s="5"/>
       <c r="G304" s="10">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="H304" s="10">
-        <v>49000</v>
+        <v>16000</v>
       </c>
       <c r="I304" s="10">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="J304" s="10">
-        <v>80000</v>
+        <v>30000</v>
       </c>
       <c r="K304" s="10">
-        <v>90000</v>
+        <v>33000</v>
       </c>
       <c r="L304" s="3" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="M304" s="3" t="s">
         <v>284</v>
@@ -12188,7 +12178,7 @@
         <v>73</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>457</v>
+        <v>402</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>43</v>
@@ -12225,7 +12215,7 @@
         <v>73</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>74</v>
+        <v>457</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>43</v>
@@ -12262,7 +12252,7 @@
         <v>73</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>458</v>
+        <v>74</v>
       </c>
       <c r="C307" s="3" t="s">
         <v>43</v>
@@ -12296,36 +12286,36 @@
     </row>
     <row r="308" spans="1:13" ht="12.75" customHeight="1">
       <c r="A308" s="3" t="s">
-        <v>116</v>
+        <v>73</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>117</v>
+        <v>458</v>
       </c>
       <c r="C308" s="3" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="E308" s="5"/>
       <c r="F308" s="5"/>
       <c r="G308" s="10">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="H308" s="10">
-        <v>16000</v>
+        <v>49000</v>
       </c>
       <c r="I308" s="10">
-        <v>18000</v>
+        <v>53000</v>
       </c>
       <c r="J308" s="10">
-        <v>30000</v>
+        <v>80000</v>
       </c>
       <c r="K308" s="10">
-        <v>33000</v>
+        <v>90000</v>
       </c>
       <c r="L308" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="M308" s="3" t="s">
         <v>284</v>
@@ -12336,13 +12326,13 @@
         <v>116</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>365</v>
+        <v>117</v>
       </c>
       <c r="C309" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E309" s="5"/>
       <c r="F309" s="5"/>
@@ -12373,13 +12363,13 @@
         <v>116</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>441</v>
+        <v>365</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>9</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="E310" s="5"/>
       <c r="F310" s="5"/>
@@ -12407,10 +12397,10 @@
     </row>
     <row r="311" spans="1:13" ht="12.75" customHeight="1">
       <c r="A311" s="3" t="s">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>118</v>
+        <v>441</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>9</v>
@@ -12444,83 +12434,97 @@
     </row>
     <row r="312" spans="1:13" ht="12.75" customHeight="1">
       <c r="A312" s="3" t="s">
-        <v>333</v>
+        <v>73</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>334</v>
+        <v>118</v>
       </c>
       <c r="C312" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D312" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E312" s="5"/>
       <c r="F312" s="5"/>
-      <c r="G312" s="10"/>
-      <c r="H312" s="10"/>
-      <c r="I312" s="10"/>
-      <c r="J312" s="10"/>
-      <c r="K312" s="10"/>
-      <c r="L312" s="3"/>
+      <c r="G312" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H312" s="10">
+        <v>16000</v>
+      </c>
+      <c r="I312" s="10">
+        <v>18000</v>
+      </c>
+      <c r="J312" s="10">
+        <v>30000</v>
+      </c>
+      <c r="K312" s="10">
+        <v>33000</v>
+      </c>
+      <c r="L312" s="3" t="s">
+        <v>85</v>
+      </c>
       <c r="M312" s="3" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="313" spans="1:13" ht="12.75" customHeight="1">
       <c r="A313" s="3" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>368</v>
+        <v>334</v>
       </c>
       <c r="C313" s="3" t="s">
-        <v>9</v>
+        <v>233</v>
       </c>
       <c r="D313" s="5"/>
       <c r="E313" s="5"/>
       <c r="F313" s="5"/>
-      <c r="G313" s="10">
-        <v>15000</v>
-      </c>
-      <c r="H313" s="10">
-        <v>17000</v>
-      </c>
-      <c r="I313" s="10">
-        <v>21000</v>
-      </c>
-      <c r="J313" s="10">
-        <v>35000</v>
-      </c>
-      <c r="K313" s="10">
-        <v>39000</v>
-      </c>
-      <c r="L313" s="3" t="s">
-        <v>363</v>
-      </c>
+      <c r="G313" s="10"/>
+      <c r="H313" s="10"/>
+      <c r="I313" s="10"/>
+      <c r="J313" s="10"/>
+      <c r="K313" s="10"/>
+      <c r="L313" s="3"/>
       <c r="M313" s="3" t="s">
-        <v>367</v>
+        <v>284</v>
       </c>
     </row>
     <row r="314" spans="1:13" ht="12.75" customHeight="1">
       <c r="A314" s="3" t="s">
-        <v>265</v>
+        <v>366</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>259</v>
+        <v>368</v>
       </c>
       <c r="C314" s="3" t="s">
-        <v>233</v>
+        <v>9</v>
       </c>
       <c r="D314" s="5"/>
       <c r="E314" s="5"/>
       <c r="F314" s="5"/>
-      <c r="G314" s="10"/>
-      <c r="H314" s="10"/>
-      <c r="I314" s="10"/>
-      <c r="J314" s="10"/>
-      <c r="K314" s="10"/>
-      <c r="L314" s="3"/>
+      <c r="G314" s="10">
+        <v>15000</v>
+      </c>
+      <c r="H314" s="10">
+        <v>17000</v>
+      </c>
+      <c r="I314" s="10">
+        <v>21000</v>
+      </c>
+      <c r="J314" s="10">
+        <v>35000</v>
+      </c>
+      <c r="K314" s="10">
+        <v>39000</v>
+      </c>
+      <c r="L314" s="3" t="s">
+        <v>363</v>
+      </c>
       <c r="M314" s="3" t="s">
-        <v>340</v>
+        <v>367</v>
       </c>
     </row>
     <row r="315" spans="1:13" ht="12.75" customHeight="1">
@@ -12528,7 +12532,7 @@
         <v>265</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C315" s="3" t="s">
         <v>233</v>
@@ -12551,7 +12555,7 @@
         <v>265</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>233</v>
@@ -12570,12 +12574,14 @@
       </c>
     </row>
     <row r="317" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A317" s="3"/>
+      <c r="A317" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="B317" s="5" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C317" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D317" s="5"/>
       <c r="E317" s="5"/>
@@ -12586,12 +12592,14 @@
       <c r="J317" s="10"/>
       <c r="K317" s="10"/>
       <c r="L317" s="3"/>
-      <c r="M317" s="3"/>
+      <c r="M317" s="3" t="s">
+        <v>340</v>
+      </c>
     </row>
     <row r="318" spans="1:13" ht="12.75" customHeight="1">
       <c r="A318" s="3"/>
       <c r="B318" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>244</v>
@@ -12610,7 +12618,7 @@
     <row r="319" spans="1:13" ht="12.75" customHeight="1">
       <c r="A319" s="3"/>
       <c r="B319" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C319" s="3" t="s">
         <v>244</v>
@@ -12629,7 +12637,7 @@
     <row r="320" spans="1:13" ht="12.75" customHeight="1">
       <c r="A320" s="3"/>
       <c r="B320" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C320" s="3" t="s">
         <v>244</v>
@@ -12646,48 +12654,30 @@
       <c r="M320" s="3"/>
     </row>
     <row r="321" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A321" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B321" s="4" t="s">
-        <v>314</v>
+      <c r="A321" s="3"/>
+      <c r="B321" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="C321" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D321" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D321" s="5"/>
       <c r="E321" s="5"/>
       <c r="F321" s="5"/>
-      <c r="G321" s="10">
-        <v>18000</v>
-      </c>
-      <c r="H321" s="10">
-        <v>20000</v>
-      </c>
-      <c r="I321" s="10">
-        <v>24000</v>
-      </c>
-      <c r="J321" s="10">
-        <v>38000</v>
-      </c>
-      <c r="K321" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L321" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M321" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="G321" s="10"/>
+      <c r="H321" s="10"/>
+      <c r="I321" s="10"/>
+      <c r="J321" s="10"/>
+      <c r="K321" s="10"/>
+      <c r="L321" s="3"/>
+      <c r="M321" s="3"/>
     </row>
     <row r="322" spans="1:13" ht="12.75" customHeight="1">
       <c r="A322" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C322" s="3" t="s">
         <v>9</v>
@@ -12724,7 +12714,7 @@
         <v>39</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C323" s="3" t="s">
         <v>9</v>
@@ -12758,72 +12748,72 @@
     </row>
     <row r="324" spans="1:13" ht="12.75" customHeight="1">
       <c r="A324" s="3" t="s">
-        <v>190</v>
+        <v>39</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>216</v>
+        <v>316</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D324" s="5">
-        <v>99</v>
+      <c r="D324" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="E324" s="5"/>
       <c r="F324" s="5"/>
       <c r="G324" s="10">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="H324" s="10">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="I324" s="10">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="J324" s="10">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="K324" s="10">
-        <v>0</v>
-      </c>
-      <c r="L324" s="3"/>
+        <v>42000</v>
+      </c>
+      <c r="L324" s="3" t="s">
+        <v>11</v>
+      </c>
       <c r="M324" s="3" t="s">
-        <v>217</v>
+        <v>12</v>
       </c>
     </row>
     <row r="325" spans="1:13" ht="12.75" customHeight="1">
       <c r="A325" s="3" t="s">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="C325" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D325" s="5" t="s">
-        <v>10</v>
+      <c r="D325" s="5">
+        <v>99</v>
       </c>
       <c r="E325" s="5"/>
       <c r="F325" s="5"/>
       <c r="G325" s="10">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="H325" s="10">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I325" s="10">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="J325" s="10">
-        <v>38000</v>
+        <v>0</v>
       </c>
       <c r="K325" s="10">
-        <v>42000</v>
-      </c>
-      <c r="L325" s="3" t="s">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L325" s="3"/>
       <c r="M325" s="3" t="s">
         <v>217</v>
       </c>
@@ -12833,7 +12823,7 @@
         <v>40</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>317</v>
+        <v>41</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>9</v>
@@ -12867,134 +12857,136 @@
     </row>
     <row r="327" spans="1:13" ht="12.75" customHeight="1">
       <c r="A327" s="3" t="s">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
       <c r="C327" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D327" s="5"/>
+        <v>9</v>
+      </c>
+      <c r="D327" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="E327" s="5"/>
       <c r="F327" s="5"/>
-      <c r="G327" s="10"/>
-      <c r="H327" s="10"/>
-      <c r="I327" s="10"/>
-      <c r="J327" s="10"/>
-      <c r="K327" s="10"/>
-      <c r="L327" s="3"/>
-      <c r="M327" s="3"/>
+      <c r="G327" s="10">
+        <v>18000</v>
+      </c>
+      <c r="H327" s="10">
+        <v>20000</v>
+      </c>
+      <c r="I327" s="10">
+        <v>24000</v>
+      </c>
+      <c r="J327" s="10">
+        <v>38000</v>
+      </c>
+      <c r="K327" s="10">
+        <v>42000</v>
+      </c>
+      <c r="L327" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M327" s="3" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="328" spans="1:13" ht="12.75" customHeight="1">
       <c r="A328" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B328" s="5" t="s">
-        <v>343</v>
+        <v>248</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>249</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="D328" s="5"/>
       <c r="E328" s="5"/>
       <c r="F328" s="5"/>
-      <c r="G328" s="10">
-        <v>13000</v>
-      </c>
-      <c r="H328" s="10">
-        <v>14000</v>
-      </c>
-      <c r="I328" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J328" s="10">
-        <v>28000</v>
-      </c>
-      <c r="K328" s="10">
-        <v>31000</v>
-      </c>
+      <c r="G328" s="10"/>
+      <c r="H328" s="10"/>
+      <c r="I328" s="10"/>
+      <c r="J328" s="10"/>
+      <c r="K328" s="10"/>
       <c r="L328" s="3"/>
-      <c r="M328" s="3" t="s">
-        <v>342</v>
-      </c>
+      <c r="M328" s="3"/>
     </row>
     <row r="329" spans="1:13" ht="12.75" customHeight="1">
       <c r="A329" s="3" t="s">
-        <v>121</v>
+        <v>341</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>122</v>
+        <v>343</v>
       </c>
       <c r="C329" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D329" s="5" t="s">
-        <v>84</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="D329" s="5"/>
       <c r="E329" s="5"/>
       <c r="F329" s="5"/>
       <c r="G329" s="10">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H329" s="10">
+        <v>14000</v>
+      </c>
+      <c r="I329" s="10">
         <v>16000</v>
       </c>
-      <c r="I329" s="10">
-        <v>18000</v>
-      </c>
       <c r="J329" s="10">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="K329" s="10">
-        <v>33000</v>
-      </c>
-      <c r="L329" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="M329" s="3"/>
+        <v>31000</v>
+      </c>
+      <c r="L329" s="3"/>
+      <c r="M329" s="3" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="330" spans="1:13" ht="12.75" customHeight="1">
       <c r="A330" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B330" s="4" t="s">
-        <v>371</v>
+        <v>121</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>122</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D330" s="5"/>
+      <c r="D330" s="5" t="s">
+        <v>84</v>
+      </c>
       <c r="E330" s="5"/>
       <c r="F330" s="5"/>
       <c r="G330" s="10">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H330" s="10">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="I330" s="10">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="J330" s="10">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="K330" s="10">
-        <v>28000</v>
-      </c>
-      <c r="L330" s="15" t="s">
-        <v>369</v>
-      </c>
-      <c r="M330" s="15" t="s">
-        <v>385</v>
-      </c>
+        <v>33000</v>
+      </c>
+      <c r="L330" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="M330" s="3"/>
     </row>
     <row r="331" spans="1:13" ht="12.75" customHeight="1">
       <c r="A331" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>442</v>
+        <v>371</v>
       </c>
       <c r="C331" s="3" t="s">
         <v>9</v>
@@ -13021,15 +13013,15 @@
         <v>369</v>
       </c>
       <c r="M331" s="15" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="12.75" customHeight="1">
       <c r="A332" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B332" s="5" t="s">
-        <v>372</v>
+      <c r="B332" s="4" t="s">
+        <v>442</v>
       </c>
       <c r="C332" s="3" t="s">
         <v>9</v>
@@ -13061,43 +13053,49 @@
     </row>
     <row r="333" spans="1:13" ht="12.75" customHeight="1">
       <c r="A333" s="3" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B333" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="C333" s="15" t="s">
-        <v>244</v>
+        <v>372</v>
+      </c>
+      <c r="C333" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="D333" s="5"/>
       <c r="E333" s="5"/>
       <c r="F333" s="5"/>
       <c r="G333" s="10">
-        <v>15000</v>
+        <v>10000</v>
       </c>
       <c r="H333" s="10">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="I333" s="10">
-        <v>18000</v>
-      </c>
-      <c r="J333" s="10"/>
-      <c r="K333" s="10"/>
+        <v>13000</v>
+      </c>
+      <c r="J333" s="10">
+        <v>25000</v>
+      </c>
+      <c r="K333" s="10">
+        <v>28000</v>
+      </c>
       <c r="L333" s="15" t="s">
         <v>369</v>
       </c>
       <c r="M333" s="15" t="s">
-        <v>387</v>
+        <v>295</v>
       </c>
     </row>
     <row r="334" spans="1:13" ht="12.75" customHeight="1">
       <c r="A334" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B334" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="C334" s="15"/>
+      <c r="B334" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C334" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="D334" s="5"/>
       <c r="E334" s="5"/>
       <c r="F334" s="5"/>
@@ -13124,29 +13122,23 @@
         <v>373</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="C335" s="15" t="s">
-        <v>244</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="C335" s="15"/>
       <c r="D335" s="5"/>
       <c r="E335" s="5"/>
       <c r="F335" s="5"/>
       <c r="G335" s="10">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H335" s="10">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="I335" s="10">
-        <v>16000</v>
-      </c>
-      <c r="J335" s="10">
-        <v>28000</v>
-      </c>
-      <c r="K335" s="10">
-        <v>31000</v>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="J335" s="10"/>
+      <c r="K335" s="10"/>
       <c r="L335" s="15" t="s">
         <v>369</v>
       </c>
@@ -13159,9 +13151,11 @@
         <v>373</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="C336" s="15"/>
+        <v>388</v>
+      </c>
+      <c r="C336" s="15" t="s">
+        <v>244</v>
+      </c>
       <c r="D336" s="5"/>
       <c r="E336" s="5"/>
       <c r="F336" s="5"/>
@@ -13188,30 +13182,42 @@
       </c>
     </row>
     <row r="337" spans="1:13" ht="12.75" customHeight="1">
-      <c r="A337" s="16"/>
-      <c r="B337" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="C337" s="15" t="s">
-        <v>244</v>
-      </c>
+      <c r="A337" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C337" s="15"/>
       <c r="D337" s="5"/>
       <c r="E337" s="5"/>
       <c r="F337" s="5"/>
-      <c r="G337" s="10"/>
-      <c r="H337" s="10"/>
-      <c r="I337" s="10"/>
-      <c r="J337" s="10"/>
-      <c r="K337" s="10"/>
-      <c r="L337" s="16"/>
+      <c r="G337" s="10">
+        <v>13000</v>
+      </c>
+      <c r="H337" s="10">
+        <v>14000</v>
+      </c>
+      <c r="I337" s="10">
+        <v>16000</v>
+      </c>
+      <c r="J337" s="10">
+        <v>28000</v>
+      </c>
+      <c r="K337" s="10">
+        <v>31000</v>
+      </c>
+      <c r="L337" s="15" t="s">
+        <v>369</v>
+      </c>
       <c r="M337" s="15" t="s">
-        <v>295</v>
+        <v>387</v>
       </c>
     </row>
     <row r="338" spans="1:13" ht="12.75" customHeight="1">
       <c r="A338" s="16"/>
       <c r="B338" s="5" t="s">
-        <v>445</v>
+        <v>374</v>
       </c>
       <c r="C338" s="15" t="s">
         <v>244</v>
@@ -13230,15 +13236,25 @@
       </c>
     </row>
     <row r="339" spans="1:13" ht="12.75" customHeight="1">
-      <c r="B339" s="1"/>
-      <c r="D339" s="1"/>
-      <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
-      <c r="G339" s="2"/>
-      <c r="H339" s="2"/>
-      <c r="I339" s="2"/>
-      <c r="J339" s="2"/>
-      <c r="K339" s="2"/>
+      <c r="A339" s="16"/>
+      <c r="B339" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C339" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="D339" s="5"/>
+      <c r="E339" s="5"/>
+      <c r="F339" s="5"/>
+      <c r="G339" s="10"/>
+      <c r="H339" s="10"/>
+      <c r="I339" s="10"/>
+      <c r="J339" s="10"/>
+      <c r="K339" s="10"/>
+      <c r="L339" s="16"/>
+      <c r="M339" s="15" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="340" spans="1:13" ht="12.75" customHeight="1">
       <c r="B340" s="1"/>
@@ -22491,9 +22507,20 @@
       <c r="J1180" s="2"/>
       <c r="K1180" s="2"/>
     </row>
+    <row r="1181" spans="2:11" ht="12.75" customHeight="1">
+      <c r="B1181" s="1"/>
+      <c r="D1181" s="1"/>
+      <c r="E1181" s="1"/>
+      <c r="F1181" s="1"/>
+      <c r="G1181" s="2"/>
+      <c r="H1181" s="2"/>
+      <c r="I1181" s="2"/>
+      <c r="J1181" s="2"/>
+      <c r="K1181" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M329">
-    <sortCondition ref="B252:B329"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M330">
+    <sortCondition ref="B253:B330"/>
   </sortState>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
